--- a/workspaces/btc_daily_14days/ma/ma_ratio_50.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_50.xlsx
@@ -575,46 +575,46 @@
         <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.345290172063514</v>
+        <v>-4.331415784882914</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.958344107426939</v>
+        <v>-5.939099916210822</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.64930551234329</v>
+        <v>-2.641006803591139</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-17.34538193646518</v>
+        <v>-17.28995224899268</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.059121096422061</v>
+        <v>-3.049617361798475</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.17866496702032</v>
+        <v>-10.14615813695843</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.847696842375811</v>
+        <v>-2.838579092099337</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.5239862500753</v>
+        <v>11.48713406553323</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.378664365974636</v>
+        <v>-3.367301665485165</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.90461489984402</v>
+        <v>6.882513587328432</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.988250689329341</v>
+        <v>2.978638845305554</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6899578518166152</v>
+        <v>-0.6881918979999355</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.602746719977866</v>
+        <v>2.59433874202103</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.28539864301756</v>
+        <v>10.25211424924375</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>34</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320208639</v>
+        <v>-2.485373772063063</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.98987617017162</v>
+        <v>-9.957229324507736</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.559455175626532</v>
+        <v>-1.554573633743594</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.42949478355127</v>
+        <v>-1.424971879984263</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.856994308966719</v>
+        <v>-7.831744681502322</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-16.39578133736541</v>
+        <v>-16.3425627940851</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-10.59359049524742</v>
+        <v>-10.55914688197505</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-16.95695010633926</v>
+        <v>-16.9017552199989</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.12848323836207</v>
+        <v>-11.09174765891433</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.087361176992268</v>
+        <v>-6.06755465835802</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.294113277879276</v>
+        <v>-6.273689001568464</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.260863861724538</v>
+        <v>-6.24095646185237</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.7842071249427818</v>
+        <v>-0.7817302821547685</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.484357807649651</v>
+        <v>-3.473375946837706</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.870198043425354</v>
+        <v>8.841060204631141</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14.08033297206162</v>
+        <v>14.03448556762773</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.68888458846902</v>
+        <v>13.64372878673494</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.273792647783736</v>
+        <v>9.243214400584776</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11.01220853361427</v>
+        <v>10.97591790664929</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>13.58825502460834</v>
+        <v>13.54394159360216</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13.50683824088195</v>
+        <v>13.4627236923595</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.04209675570919</v>
+        <v>12.99974930313144</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>15.26136292202168</v>
+        <v>15.21205838389368</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>12.13566532209521</v>
+        <v>12.09594871578437</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>18.7689634319143</v>
+        <v>18.70738798549365</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.08761439036375</v>
+        <v>21.01799790553666</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>18.39159148944307</v>
+        <v>18.3310708137024</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>20.92723703795301</v>
+        <v>20.85817485530266</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.747169663492876</v>
+        <v>-1.767075030979193</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3737597873677672</v>
+        <v>-0.3780170261942999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.711086082585602</v>
+        <v>3.758066762912449</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.336083922643652</v>
+        <v>5.401775061832936</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.30445990010351</v>
+        <v>3.345956594973501</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.603034397387184</v>
+        <v>3.64681260525419</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.024294867380497</v>
+        <v>2.049343921038414</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.433796248100151</v>
+        <v>-1.451250773438979</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.495770273223243</v>
+        <v>1.512564153917786</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.843560154520311</v>
+        <v>-3.888804232546647</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.432352415238903</v>
+        <v>3.475617994819231</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.022119467747963</v>
+        <v>-1.030531581906075</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.5501489079642</v>
+        <v>1.571431860434679</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.640869998208416</v>
+        <v>2.676356673485181</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5453863721580348</v>
+        <v>-0.5503301177165696</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.755607256077148</v>
+        <v>-4.804133147328507</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.553029417708771</v>
+        <v>-2.576435675013244</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.123582265039637</v>
+        <v>-1.132783219949928</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.537442020104983</v>
+        <v>3.575769017537311</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.737344221687906</v>
+        <v>7.817568760900443</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.353777683808353</v>
+        <v>6.419776862519846</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.188265004902021</v>
+        <v>7.261374065863315</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.430385576031554</v>
+        <v>8.515892134239834</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.675325295125518</v>
+        <v>3.713075503404781</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.73690311000459</v>
+        <v>-1.752323807079961</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.005046674340221</v>
+        <v>-3.032623777288201</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.296855009095523</v>
+        <v>-5.348484276016677</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-8.9581782894684</v>
+        <v>-9.046131364793027</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.357801349211506</v>
+        <v>5.58182480510628</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.212801058377302</v>
+        <v>-1.266432908385006</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.627718114902436</v>
+        <v>4.828422943050171</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.202986209879974</v>
+        <v>-0.2028513039336275</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5407334495020635</v>
+        <v>0.5748736216977264</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.197489507704994</v>
+        <v>-1.236263859293452</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.588086424166988</v>
+        <v>-4.768691910167433</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.869726522960683</v>
+        <v>-6.108602676487962</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.103149916912578</v>
+        <v>-5.310536536774627</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.934762808624406</v>
+        <v>-6.17684323100795</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.01753960650732</v>
+        <v>-4.17563460100147</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.694745889482434</v>
+        <v>-2.795743276687027</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.094068399452425</v>
+        <v>-3.215997887631929</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.28310352814114</v>
+        <v>1.344068272230572</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.86422483706378</v>
+        <v>-6.060769228567224</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.55315836618508</v>
+        <v>-1.611696087943947</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.195827409129024</v>
+        <v>-4.32899328669599</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9520626040571614</v>
+        <v>-0.9780757949879657</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.13236963195741</v>
+        <v>4.287364451643661</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.190603919915119</v>
+        <v>-1.224101085678697</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.089519508906797</v>
+        <v>-2.15950408745249</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.797332492953842</v>
+        <v>-2.898000849865234</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.108547393241345</v>
+        <v>-3.21941424959963</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.056445726993815</v>
+        <v>-3.166672227597786</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.383879328442411</v>
+        <v>-4.53421624958979</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.915870066339991</v>
+        <v>-5.081228441081301</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.879617860358287</v>
+        <v>-6.082878400863677</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.329933442297495</v>
+        <v>-7.577343115099026</v>
       </c>
     </row>
     <row r="13">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.2667</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4046~4059</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4046</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.04209562496484409</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.2427</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4019~4032</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4019</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.01327959005124058</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.2187</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3985~3998</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3985</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.00781230510268216</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.1947</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3941~3954</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3941</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.09080807235969246</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1707</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3875~3887</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3875</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.06225746093547002</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.1467</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3799~3810</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3799</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.05249343832021225</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.1227</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3683~3689</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3683</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.2299522806328511</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.09871</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3511~3511</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3511</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.05569298141348611</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.07472</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3315~3315</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3315</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.02541537511431358</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.05072</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3054~3054</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3054</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.1260770694429425</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.02673</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2730~2730</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2730</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.6933748666032145</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.002739</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2396~2396</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2396</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.429767022027079</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.02125</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2073~2073</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2073</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>2.11341165567039</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.04525</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1791~1791</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1791</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.777918463709625</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.06924</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1479~1479</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1479</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.949428481683199</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.09323</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1245~1245</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1245</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>3.00856971191854</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.1172</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1040~1040</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1040</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.891177064405412</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.1412</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>884~884</t>
-        </is>
+      <c r="B23" t="n">
+        <v>884</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.823303761237995</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.1652</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>746~746</t>
-        </is>
+      <c r="B24" t="n">
+        <v>746</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.600395459950889</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.1892</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>605~605</t>
-        </is>
+      <c r="B25" t="n">
+        <v>605</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.721437712847873</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.2132</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>473~473</t>
-        </is>
+      <c r="B26" t="n">
+        <v>473</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.052016225244564</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.2372</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>390~390</t>
-        </is>
+      <c r="B27" t="n">
+        <v>390</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.147587320815667</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.2612</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>337~337</t>
-        </is>
+      <c r="B28" t="n">
+        <v>337</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.809232302935428</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.2852</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>288~288</t>
-        </is>
+      <c r="B29" t="n">
+        <v>288</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.367672790901139</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.3092</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>239~239</t>
-        </is>
+      <c r="B30" t="n">
+        <v>239</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.899867119120564</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.3332</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>193~193</t>
-        </is>
+      <c r="B31" t="n">
+        <v>193</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.428841472536135</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.3571</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>152~152</t>
-        </is>
+      <c r="B32" t="n">
+        <v>152</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.453930100842655</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.3811</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>120~120</t>
-        </is>
+      <c r="B33" t="n">
+        <v>120</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.673228346456689</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.4051</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>102~102</t>
-        </is>
+      <c r="B34" t="n">
+        <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.408522464103754</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.4291</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B35" t="n">
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>4.133067703886418</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.2667</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5.337886980994838</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.2427</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>110~110</t>
-        </is>
+      <c r="B7" t="n">
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.961107134335478</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.2187</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>144~144</t>
-        </is>
+      <c r="B8" t="n">
+        <v>144</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.673228346456689</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.1947</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>188~188</t>
-        </is>
+      <c r="B9" t="n">
+        <v>188</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3.357625509577254</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1707</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>254~255</t>
-        </is>
+      <c r="B10" t="n">
+        <v>254</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2.01636560135865</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.1467</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>330~332</t>
-        </is>
+      <c r="B11" t="n">
+        <v>330</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1.422224330392439</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.1227</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>446~453</t>
-        </is>
+      <c r="B12" t="n">
+        <v>446</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2.473449097008569</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.09871</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>618~631</t>
-        </is>
+      <c r="B13" t="n">
+        <v>618</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.1214586686965262</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.07472</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>814~827</t>
-        </is>
+      <c r="B14" t="n">
+        <v>814</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.2272388261019955</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.05072</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1075~1088</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1075</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.1037324378570332</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.02673</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1399~1412</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1399</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.14782925505417</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.002739</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1733~1746</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1733</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.80615309684228</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.02125</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2056~2069</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2056</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.985946778402337</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.04525</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2338~2351</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2338</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.238653122421795</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.06924</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2650~2663</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2650</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.535871666060523</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.09323</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2884~2897</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2884</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.19899579345816</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.1172</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3089~3102</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3089</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.8815750062190091</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.1412</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3245~3258</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3245</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.6825113711614819</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.1652</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3383~3396</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3383</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.4910826076069128</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.1892</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3524~3537</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3524</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.217498258010373</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.2132</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3656~3669</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3656</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.1903584619379686</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.2372</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3739~3752</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3739</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.2546323500607244</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.2612</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3792~3805</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3792</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.08870770260156746</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.2852</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3841~3854</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3841</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1063080659287081</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.3092</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3890~3903</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3890</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.0466025528515317</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.3332</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3936~3949</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3936</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.04978169828036982</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.3571</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3977~3990</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3977</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.01282734395042695</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.3811</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4009~4022</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4009</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.01775014324104518</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.4051</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4027~4040</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4027</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.006561679790024755</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.4291</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4046~4059</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4046</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.01745901496237678</v>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_50.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_50.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-50 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-50 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.2547</t>
+          <t>X ≈ -0.2546</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.331415784882914</v>
+        <v>-4.318938578775445</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.939099916210822</v>
+        <v>-5.926234191469952</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.641006803591139</v>
+        <v>-2.628038012552594</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-17.28995224899268</v>
+        <v>-17.27701684700544</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.049617361798475</v>
+        <v>-3.036538369158244</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.14615813695843</v>
+        <v>-10.13314690737986</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.838579092099337</v>
+        <v>-2.825537500642483</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.48713406553323</v>
+        <v>11.50029898132983</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.367301665485165</v>
+        <v>-3.354120986996605</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.882513587328432</v>
+        <v>6.895906633346286</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.978638845305554</v>
+        <v>2.992086326725016</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6881918979999355</v>
+        <v>-0.6747465667879737</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.59433874202103</v>
+        <v>2.607891468284116</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.25211424924375</v>
+        <v>10.24168461354223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.2307</t>
+          <t>X ≈ -0.2306</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>34</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.485373772063063</v>
+        <v>-2.472895800829747</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.957229324507736</v>
+        <v>-9.944367366865237</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.554573633743594</v>
+        <v>-1.541604704428472</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.424971879984263</v>
+        <v>-1.412027346140952</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.831744681502322</v>
+        <v>-7.818668903260992</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-16.3425627940851</v>
+        <v>-16.32955523935048</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-10.55914688197505</v>
+        <v>-10.54610908251234</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-16.9017552199989</v>
+        <v>-16.88860119222288</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.09174765891433</v>
+        <v>-11.07856970166874</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.06755465835802</v>
+        <v>-6.054165028801194</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.273689001568464</v>
+        <v>-6.260243407830814</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.24095646185237</v>
+        <v>-6.227511936913409</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.7817302821547685</v>
+        <v>-0.7681778166978148</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.473375946837706</v>
+        <v>-3.483805582533186</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.841060204631141</v>
+        <v>8.853546708239932</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14.03448556762773</v>
+        <v>14.04736490609584</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.64372878673494</v>
+        <v>13.65670767292125</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.243214400584776</v>
+        <v>9.256165083575254</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.97591790664929</v>
+        <v>10.98900377670402</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>13.54394159360216</v>
+        <v>13.55696364530733</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13.4627236923595</v>
+        <v>13.47577164149988</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.99974930313144</v>
+        <v>13.01291420096678</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>15.21205838389368</v>
+        <v>15.22524431463195</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>12.09594871578437</v>
+        <v>12.10934268035196</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>18.70738798549365</v>
+        <v>18.72083814460964</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.01799790553666</v>
+        <v>21.03144576905036</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>18.3310708137024</v>
+        <v>18.34462443732961</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>20.85817485530266</v>
+        <v>20.84774521960451</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.767075030979193</v>
+        <v>-1.729153429793747</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3780170261942999</v>
+        <v>-0.3597076970814399</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.758066762912449</v>
+        <v>3.710982436414284</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.401775061832936</v>
+        <v>5.330749490347266</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.345956594973501</v>
+        <v>3.305992102399316</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.64681260525419</v>
+        <v>3.603867270348047</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.049343921038414</v>
+        <v>2.030365980483694</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.451250773438979</v>
+        <v>-1.415779824184057</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.512564153917786</v>
+        <v>1.504277670403802</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.888804232546647</v>
+        <v>-3.817579215544477</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.475617994819231</v>
+        <v>3.433758596235087</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.030531581906075</v>
+        <v>-1.00633349196162</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.571431860434679</v>
+        <v>1.557778325398395</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.676356673485181</v>
+        <v>3.276510484189998</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>76</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5503301177165696</v>
+        <v>-0.5375453405354165</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.804133147328507</v>
+        <v>-4.789823528248455</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.576435675013244</v>
+        <v>-2.562675364763074</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.132783219949928</v>
+        <v>-1.119415527105879</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.575769017537311</v>
+        <v>3.588041228407711</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.817568760900443</v>
+        <v>7.828689229962571</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.419776862519846</v>
+        <v>6.431293281422739</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.261374065863315</v>
+        <v>7.272825898865413</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.515892134239834</v>
+        <v>8.527043475264414</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.713075503404781</v>
+        <v>3.725678989889012</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.752323807079961</v>
+        <v>-1.738283518516809</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.032623777288201</v>
+        <v>-3.01826904216724</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.348484276016677</v>
+        <v>-6.07701176668111</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-9.046131364793027</v>
+        <v>-9.056561000491179</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>116</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.58182480510628</v>
+        <v>5.143693475028208</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.266432908385006</v>
+        <v>-1.252568545371446</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.828422943050171</v>
+        <v>4.374723553975542</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2028513039336275</v>
+        <v>-0.1894025618888264</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5748736216977264</v>
+        <v>0.1180750258346634</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.236263859293452</v>
+        <v>-1.690889759000648</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.768691910167433</v>
+        <v>-4.754162656067102</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-6.108602676487962</v>
+        <v>-6.093554170720935</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.310536536774627</v>
+        <v>-5.295680428524236</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.17684323100795</v>
+        <v>-6.161535609537204</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.17563460100147</v>
+        <v>-4.645362133998667</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.795743276687027</v>
+        <v>-3.264822748402594</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.215997887631929</v>
+        <v>-3.202441841280326</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.344068272230572</v>
+        <v>1.33363863653242</v>
       </c>
     </row>
     <row r="12">
@@ -887,462 +887,462 @@
         <v>172</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.060769228567224</v>
+        <v>-6.048246938891602</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.611696087943947</v>
+        <v>-1.913563791536227</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.32899328669599</v>
+        <v>-4.315986155278388</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9780757949879657</v>
+        <v>-1.279572493302261</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.287364451643661</v>
+        <v>4.300475256018601</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.224101085678697</v>
+        <v>-1.211058189384332</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.15950408745249</v>
+        <v>-2.463605259658728</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.898000849865234</v>
+        <v>-3.205785243863247</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.21941424959963</v>
+        <v>-3.527512892930545</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.166672227597786</v>
+        <v>-3.479789080602892</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.53421624958979</v>
+        <v>-4.520758955879572</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.081228441081301</v>
+        <v>-5.067776152361191</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-6.082878400863677</v>
+        <v>-6.069322354512074</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.577343115099026</v>
+        <v>-7.587772750797178</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.08672</t>
+          <t>X ≈ -0.08669</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.567786169585716</v>
+        <v>0.0443364947179461</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.57439968827628</v>
+        <v>-2.576950608446666</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.112364258188364</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2879948541020951</v>
+        <v>-0.3162443243608166</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.8264160691741509</v>
+        <v>-0.8545338774563973</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.001638113439355</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.9169043961669487</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.61150349241035</v>
+        <v>-2.62409036602584</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6316870520620341</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.012424481987921</v>
+        <v>-3.029940813827977</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1559533165095885</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.182794648960069</v>
+        <v>-3.200263819732847</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.603049259904971</v>
+        <v>-3.620414673046255</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.863532009261341</v>
+        <v>-3.394679022819602</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.06272</t>
+          <t>X ≈ -0.0627</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.152442151627511</v>
+        <v>-0.7434642930825319</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.062866339304506</v>
+        <v>-5.057353088849148</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-7.373443858161629</v>
+        <v>-7.382626404106112</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.112922526320403</v>
+        <v>-1.074795082911571</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.268201978940475</v>
+        <v>-1.226984249906884</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.353901803676912</v>
+        <v>-1.315710606372178</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.971202570757534</v>
+        <v>-2.944822510039899</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3732518699222709</v>
+        <v>-0.3230880650235477</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.098315293703855</v>
+        <v>1.160331322855221</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6313318711280402</v>
+        <v>0.6965129126257494</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.342287359070987</v>
+        <v>2.808414070967878</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.227245229060102</v>
+        <v>1.298390678921649</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8069906181152007</v>
+        <v>0.8782398256082402</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.589279000199916</v>
+        <v>2.262276634135851</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03873</t>
+          <t>X ≈ -0.03871</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>324</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.653932147370469</v>
+        <v>-4.641409857694846</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.796369957865586</v>
+        <v>-3.783460148289535</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.339386812610329</v>
+        <v>-2.326379681192726</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.838763309632455</v>
+        <v>-6.825784167233991</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.833974648161416</v>
+        <v>-5.820863843786476</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.23855037833539</v>
+        <v>-6.225484124034914</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.23659797464768</v>
+        <v>-4.223416965352442</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.458091687990482</v>
+        <v>-6.444892949035719</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.765006996475194</v>
+        <v>-5.751601868822362</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.661118345484134</v>
+        <v>-5.647661051773916</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.774883336286855</v>
+        <v>-3.761431047566745</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.726002144762617</v>
+        <v>-1.712446098411014</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.871342540881393</v>
+        <v>-4.881772176579545</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01473</t>
+          <t>X ≈ -0.01472</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>334</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.589246703443443</v>
+        <v>-4.57672441376782</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.703814328383814</v>
+        <v>-4.690904518807763</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-10.48790459186663</v>
+        <v>-10.47489746044903</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-10.05825026165434</v>
+        <v>-10.04527111925588</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-9.997869081516932</v>
+        <v>-9.984758277141992</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-9.999828341406058</v>
+        <v>-9.986785445111693</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-11.88096924430708</v>
+        <v>-11.86790299000661</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-9.354140667040674</v>
+        <v>-9.340959657745437</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-9.71454175082777</v>
+        <v>-9.701343011873007</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-9.367062145436535</v>
+        <v>-9.353657017783704</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-10.17061786496369</v>
+        <v>-10.15716057125347</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-9.238031114803896</v>
+        <v>-9.224578826083786</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-10.85589051616795</v>
+        <v>-10.84233446981635</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-10.00736678868208</v>
+        <v>-10.01779642438024</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.009255</t>
+          <t>X ≈ 0.009272</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.957834605039771</v>
+        <v>-3.098199981151708</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.07455463029326381</v>
+        <v>-0.07975644458583986</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3203140763034042</v>
+        <v>-0.1658858540322328</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4291341027437952</v>
+        <v>0.581623240173414</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2003104108914471</v>
+        <v>0.3519756623863586</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.979027837151413</v>
+        <v>-1.819786110447751</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.134968984764249</v>
+        <v>-0.9785705437878605</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.292554860325929</v>
+        <v>-1.136997212266031</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.35355474650823</v>
+        <v>-1.197979368788729</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.513277454755979</v>
+        <v>-2.356540140427299</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.718030779073622</v>
+        <v>-2.561241298687492</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.754855052068685</v>
+        <v>-1.600937220406252</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.865512139793701</v>
+        <v>-1.71244609841095</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.06780319141841318</v>
+        <v>0.05649942835871968</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.03325</t>
+          <t>X ≈ 0.03327</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.244150332272298</v>
+        <v>4.458585748825087</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.568746932073992</v>
+        <v>1.779783997398255</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.946927870867562</v>
+        <v>2.808500157127213</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.72257107439696</v>
+        <v>2.582853414594581</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.361949431455436</v>
+        <v>-1.514154999711167</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7098975646616736</v>
+        <v>-0.8609090839549225</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.333028292534131</v>
+        <v>1.189611873504731</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.325644467949495</v>
+        <v>-2.480303745370904</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.386644354131796</v>
+        <v>-2.541285901893758</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.527549681003691</v>
+        <v>-2.679460925981545</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.086912934399216</v>
+        <v>-3.240033970362738</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.116359564287897</v>
+        <v>-4.273271476370397</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.18200424615479</v>
+        <v>-4.337550443562812</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.996112701112544</v>
+        <v>-5.179430451699268</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.05724</t>
+          <t>X ≈ 0.05726</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.77548960226126</v>
+        <v>-3.599126893154128</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.181935010097305</v>
+        <v>-2.01542480730425</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.307811667921527</v>
+        <v>0.4652031689630789</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.728601866137687</v>
+        <v>-3.557926320036422</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.664458978645676</v>
+        <v>-2.498771783675181</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1970855231725182</v>
+        <v>0.3545127890908333</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.394403087951481</v>
+        <v>1.547757701390154</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.888758150708441</v>
+        <v>2.039155511277535</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.186732623500461</v>
+        <v>1.339195718972015</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.298145900011029</v>
+        <v>1.128254558424899</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.13185411415499</v>
+        <v>0.2845757643819624</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.166237271500421</v>
+        <v>0.3189539167372857</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.028033942606697</v>
+        <v>1.176758334989337</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.598268095395916</v>
+        <v>1.721982803107309</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.08124</t>
+          <t>X ≈ 0.08125</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.634766807995156</v>
+        <v>2.454706287062173</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1684923403300402</v>
+        <v>-0.0148489047140572</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2263763662665994</v>
+        <v>-0.4096202894690961</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.7085796952369634</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.061894876081645</v>
+        <v>-1.246869248332658</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3371025110156509</v>
+        <v>-0.5203106693413986</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4328646264130214</v>
+        <v>0.2533480701049342</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.889019627069338</v>
+        <v>-1.072089672394249</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.6594212226533</v>
+        <v>-2.84981002634192</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.936896835031696</v>
+        <v>-3.69972882267178</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.859598877297955</v>
+        <v>-3.046060882219471</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-4.961967856704753</v>
+        <v>-5.157605476645365</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.091624177051273</v>
+        <v>-7.294494527383669</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.269253272125461</v>
+        <v>-7.497943426513359</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>205</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.604122655399784</v>
+        <v>3.616644945075407</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.968158798533082</v>
+        <v>2.981068608109133</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6220705797413757</v>
+        <v>0.6350777111589778</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.215738346495208</v>
+        <v>2.228717488893672</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.165122009471823</v>
+        <v>2.178232813846762</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.02353955694364629</v>
+        <v>0.03658245323801168</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.865635107963982</v>
+        <v>2.878701362264458</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.398451709182424</v>
+        <v>2.411632718477662</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.752085969341593</v>
+        <v>5.765284708296356</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>7.828790052606408</v>
+        <v>7.842195180259239</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.672817216093648</v>
+        <v>5.686274509803866</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.219395495390408</v>
+        <v>5.232847784110518</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.823531128347831</v>
+        <v>3.837087174699434</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>156</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.275792449020763</v>
+        <v>3.288314738696386</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.946270118107819</v>
+        <v>2.95917992768387</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.910375770485587</v>
+        <v>1.923382901903189</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.16449930203504</v>
+        <v>-1.151520159636576</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.066310252123486</v>
+        <v>4.079421056498425</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>7.568880394967351</v>
+        <v>7.581923291261717</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9.407223600771992</v>
+        <v>9.420289855072468</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.016963278913636</v>
+        <v>7.030144288208874</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>8.879040315808261</v>
+        <v>8.892239054763024</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>7.38788948975462</v>
+        <v>7.401294617407451</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>7.824161806462683</v>
+        <v>7.837619100172901</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>7.217519322782472</v>
+        <v>7.230971611502582</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9.361367275940218</v>
+        <v>9.374923322291821</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>8.970062967190785</v>
+        <v>8.959633331492633</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.028300810224806</v>
+        <v>4.040823099900429</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.09432225877994</v>
+        <v>7.107329390197542</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7.949213072546748</v>
+        <v>7.962192214945212</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.961516495155848</v>
+        <v>5.974627299530788</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>5.534320751712102</v>
+        <v>5.547363648006467</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.449587034439823</v>
+        <v>5.462653288740299</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>8.605592041455367</v>
+        <v>8.618773050750605</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>6.370679111794807</v>
+        <v>6.38387785074957</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>9.143742332563988</v>
+        <v>9.157147460216819</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.489713645927559</v>
+        <v>7.503170939637776</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.074821440954153</v>
+        <v>6.088273729674263</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.103842192328088</v>
+        <v>7.117398238679691</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.904288162285539</v>
+        <v>5.893858526587387</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>141</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>6.371809906740417</v>
+        <v>6.38433219641604</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>10.43399515902436</v>
+        <v>10.44690496860041</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.03912645242772</v>
+        <v>10.05213358384533</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.332500152411143</v>
+        <v>7.345479294809607</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.794078937338931</v>
+        <v>6.80718974171387</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7.091520875054591</v>
+        <v>7.104563771348957</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.879127583314194</v>
+        <v>4.89219383761467</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.121164042688797</v>
+        <v>5.134345051984035</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.769384014662528</v>
+        <v>5.782582753617291</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.756138262258716</v>
+        <v>7.769543389911547</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.842165079785111</v>
+        <v>6.855622373495329</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>9.004207811598633</v>
+        <v>9.017660100318743</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.874733342497699</v>
+        <v>7.888289388849302</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>8.124454674773986</v>
+        <v>8.114025039075834</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>132</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5368647100930986</v>
+        <v>0.5493869997687213</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.227153367043506</v>
+        <v>-2.214146235625904</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.175827038291267</v>
+        <v>0.1888061806897312</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.152557338370606</v>
+        <v>1.165668142745545</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.449999276086224</v>
+        <v>1.46304217238059</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.637992831541268</v>
+        <v>3.651059085841744</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.443536705486956</v>
+        <v>5.456717714782194</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.140112576880455</v>
+        <v>6.153311315835218</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.289987391852527</v>
+        <v>5.303392519505358</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.600385582686414</v>
+        <v>6.613842876396632</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.634768740031888</v>
+        <v>6.648221028751998</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.729665644238501</v>
+        <v>7.743221690590104</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>83</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.09584795876426</v>
+        <v>-3.083325669088637</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.092963740403142</v>
+        <v>-1.080053930827091</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.741083215650761</v>
+        <v>5.754090347068363</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.076155625366731</v>
+        <v>7.089134767765195</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10.15219224161983</v>
+        <v>10.16530304599477</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.039995625118692</v>
+        <v>8.053038521413058</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.160081184954841</v>
+        <v>9.173147439255317</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.692897786173447</v>
+        <v>8.706078795468684</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>11.04153645420795</v>
+        <v>11.05473519316271</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>11.39623054628845</v>
+        <v>11.40963567394128</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>12.39629649907937</v>
+        <v>12.40975379278959</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>12.43067965642473</v>
+        <v>12.44413194514484</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>16.82970215391357</v>
+        <v>16.84325820026517</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>13.46496565486456</v>
+        <v>13.4545360191664</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>53</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>11.65750507601643</v>
+        <v>11.67002736569206</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>10.04593146305218</v>
+        <v>10.05884127262823</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.53785520928584</v>
+        <v>11.55086234070344</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>17.32848570038384</v>
+        <v>17.34146484278231</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>9.242894673990975</v>
+        <v>9.256005478365914</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.65354415887645</v>
+        <v>7.666587055170815</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11.34239534726455</v>
+        <v>11.35546160156503</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10.87521194848299</v>
+        <v>10.88839295777823</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.153834703810126</v>
+        <v>5.16703344276489</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5301246131218207</v>
+        <v>0.5435297407746518</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3253712888041846</v>
+        <v>0.3388285825144024</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.020131804640236</v>
+        <v>6.033584093360346</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.48666964652552</v>
+        <v>7.500225692877123</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.736390978801808</v>
+        <v>7.725961343103656</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>49</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.473030156944667</v>
+        <v>-1.460507867269044</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.119477862744134</v>
+        <v>7.132387672320185</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.724609156147544</v>
+        <v>6.737616287565146</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.895678615285661</v>
+        <v>8.908657757684125</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.275624747152264</v>
+        <v>4.288735551527203</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.654699337929152</v>
+        <v>8.667742234223518</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.634116011996191</v>
+        <v>-1.621049757695715</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.061965895344755</v>
+        <v>6.075146904639993</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>12.12341498875428</v>
+        <v>12.13661372770905</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>17.39573878331821</v>
+        <v>17.40914391097104</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>15.15016913247007</v>
+        <v>15.16362642618029</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>17.22536861634606</v>
+        <v>17.23882090506617</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>20.88674665846238</v>
+        <v>20.90030270481398</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>17.05483533767745</v>
+        <v>17.04440570197929</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>49</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.649418822647235</v>
+        <v>4.661941112322857</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-9.207052749500761</v>
+        <v>-9.19414293992471</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.765425482678161</v>
+        <v>8.778432614095763</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.895678615285597</v>
+        <v>8.908657757684061</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.275624747152207</v>
+        <v>4.288735551527147</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>10.69551566445971</v>
+        <v>10.70855856075407</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.65159827371809</v>
+        <v>12.66466452801856</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>14.2252312014672</v>
+        <v>14.23841221076244</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>12.12341498875423</v>
+        <v>12.13661372770899</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.35492245678759</v>
+        <v>15.36832758444042</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.986903826347501</v>
+        <v>7.000361120057718</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.14373596328477</v>
+        <v>13.15718825200488</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.80511400540116</v>
+        <v>16.81867005175276</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>23.17728431726933</v>
+        <v>23.16685468157117</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>46</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.319525276731774</v>
+        <v>-0.3070029870561513</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.938466327695338</v>
+        <v>8.951376137271389</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.152054552814306</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.499937710228011</v>
+        <v>6.512916852626475</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>12.48325562559066</v>
+        <v>12.4963664299656</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.3024366937411</v>
+        <v>19.31547959003547</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.21770297646875</v>
+        <v>19.23076923076923</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>18.75051957768725</v>
+        <v>18.76370058698249</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>16.51560664802675</v>
+        <v>16.52880538698152</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>15.6654814629988</v>
+        <v>15.67888659065163</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.286815095203</v>
+        <v>13.30027238891321</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.625546078635374</v>
+        <v>4.638998367355484</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.553117554646938</v>
+        <v>8.566673600998541</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.97675193040142</v>
+        <v>10.96632229470327</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>41</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.043147045643678</v>
+        <v>6.055669335319301</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.992549042435485</v>
+        <v>2.005458852011536</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.597680335838895</v>
+        <v>1.610687467256497</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.605982248934268</v>
+        <v>6.618961391332732</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.628536643618133</v>
+        <v>3.641647447993073</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.365002971577759</v>
+        <v>6.378045867872125</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.036803916426251</v>
+        <v>-1.023737662125775</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.9350370750361492</v>
+        <v>0.948218084331387</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.313061579097742</v>
+        <v>3.326260318052505</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.780009564801489</v>
+        <v>9.79341469245432</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.136231850240044</v>
+        <v>7.149689143950262</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.609639397829383</v>
+        <v>9.623091686549493</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.750360396640573</v>
+        <v>6.763916442992176</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.122032948429087</v>
+        <v>2.111603312730935</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>32</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6315616797900248</v>
+        <v>0.6440839694656475</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.269988066825789</v>
+        <v>5.28289787640184</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.00011936022922</v>
+        <v>8.013126491646823</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>17.50537249283668</v>
+        <v>17.51835163523514</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.591951277764572</v>
+        <v>7.605062082139511</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.485606784519852</v>
+        <v>-1.472563888225487</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.57034050179211</v>
+        <v>-1.557274247491634</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.287523900573589</v>
+        <v>-8.274342891278351</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.47352378675591</v>
+        <v>-11.46032504780115</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.27840229610144</v>
+        <v>-6.264945002391222</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-12.49401913875601</v>
+        <v>-12.4805668500359</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-16.03927374970089</v>
+        <v>-16.02571770334929</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-18.91455241742464</v>
+        <v>-18.9249820531228</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>18</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.006099177936917</v>
+        <v>7.019008987512969</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.741483603947792</v>
+        <v>6.754462746346256</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.75861794443114</v>
+        <v>11.77172874880608</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.9449487710356834</v>
+        <v>0.9579916673300488</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.415770609319004</v>
+        <v>6.42883686361948</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.50414276609302</v>
+        <v>11.51732377538826</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.887587324355202</v>
+        <v>5.900786063309965</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6884635832003951</v>
+        <v>-0.6750112944802851</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.108718194145375</v>
+        <v>-1.095162147793772</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.8589968618690875</v>
+        <v>-0.8694264975672397</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>19</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.125017267578436</v>
+        <v>-5.112494977902813</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.736590880542657</v>
+        <v>-6.723681070966606</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.65801409707128</v>
+        <v>8.671021228488883</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.78826722967878</v>
+        <v>8.801246372077244</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>18.77616180408026</v>
+        <v>18.7892726084552</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.199396340313157</v>
+        <v>3.212462594613633</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.995370836268492</v>
+        <v>8.00855184556373</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.671213055349355</v>
+        <v>2.684411794304118</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.821087870321428</v>
+        <v>1.834492997974259</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.879492440740727</v>
+        <v>6.892949734450944</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.61244019138757</v>
+        <v>-3.59898790266746</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.493620987141256</v>
+        <v>6.507177033492859</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.480184424680694</v>
+        <v>1.469754788982542</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-50 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-50 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,157 +2210,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.2667</t>
+          <t>X &gt; -0.2666</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.04209562496484409</v>
+        <v>-0.04249238521415322</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01031581448471286</v>
+        <v>0.009893441812018011</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.07542907457487047</v>
+        <v>-0.07583358720980016</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1536511758023735</v>
+        <v>-0.1540355967096474</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1115012499790211</v>
+        <v>-0.1119004425153847</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.09654659705066138</v>
+        <v>-0.09694736541412396</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01979152572499743</v>
+        <v>-0.02021208666283059</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.09413947553694868</v>
+        <v>0.09368696315043934</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1455208935699304</v>
+        <v>0.1450550114288589</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.04980781833962311</v>
+        <v>0.04935872313632927</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.007100297131472644</v>
+        <v>0.006659935880399814</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1422404826295107</v>
+        <v>-0.1426439060991029</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.005019981477516922</v>
+        <v>-0.005460786353239655</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.03788410304002099</v>
+        <v>-0.03753456115340015</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.2427</t>
+          <t>X &gt; -0.2426</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4019</v>
+        <v>4020</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01327959005124058</v>
+        <v>-0.01376998540665397</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05028451931894296</v>
+        <v>0.04976295576690148</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05819329485767355</v>
+        <v>-0.05869191569630772</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.0385279787443622</v>
+        <v>-0.0390304987598924</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.0917627242215886</v>
+        <v>-0.09225735196331186</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.0290324115374645</v>
+        <v>-0.02954005505764457</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0008546597652809851</v>
+        <v>-0.00137034880774678</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.01760032302887993</v>
+        <v>0.01707538989401058</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1691203484329478</v>
+        <v>0.1685569397764937</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.003905092347402217</v>
+        <v>0.003374446127445196</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01286276353055626</v>
+        <v>-0.01339143540138821</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.138572732389413</v>
+        <v>-0.1390700822586481</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.02248270492476223</v>
+        <v>-0.02301315224259071</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1070132285716525</v>
+        <v>-0.1065740929237506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.2187</t>
+          <t>X &gt; -0.2186</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3985</v>
+        <v>3986</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.00781230510268216</v>
+        <v>0.007205999973272981</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1356685772085555</v>
+        <v>0.1350114331802104</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.04542618531636577</v>
+        <v>-0.04604288538599377</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.0266988463372968</v>
+        <v>-0.02731903543552505</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02572523700764862</v>
+        <v>-0.02635218569534459</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1101545478117458</v>
+        <v>0.1094967026608629</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.08922863648444235</v>
+        <v>0.08857473823338324</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.161956179606797</v>
+        <v>0.1612783512065974</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2651980177553668</v>
+        <v>0.2644932934666997</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.05570675646885803</v>
+        <v>0.05504437642036208</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.04055457451041633</v>
+        <v>0.03989330294848514</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.0865072250363923</v>
+        <v>-0.08713655916325536</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.01600480840635754</v>
+        <v>-0.01665700608316456</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.078291438754583</v>
+        <v>-0.07776679973590461</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3941</v>
+        <v>3942</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.09080807235969246</v>
+        <v>-0.09153549956090501</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01950725318435076</v>
+        <v>-0.02027612460981487</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1982612065724467</v>
+        <v>-0.1989908875588853</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1301944522405165</v>
+        <v>-0.1309398627405614</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1485550513494189</v>
+        <v>-0.1493039011559176</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.03982937251679886</v>
+        <v>-0.04060186290900702</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.06008214312949178</v>
+        <v>-0.0608511023916094</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01862634011552444</v>
+        <v>0.01783036100125912</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.09832111947824984</v>
+        <v>0.09750368288037947</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.0787186802755997</v>
+        <v>-0.07950385426786255</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1678546287586187</v>
+        <v>-0.1686205410477299</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3221322505997648</v>
+        <v>-0.3228589392853749</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2208440185999194</v>
+        <v>-0.2216028162075148</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3120403646461156</v>
+        <v>-0.3113341586529472</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3875</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.06225746093547002</v>
+        <v>-0.06322055728332998</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01340102221180217</v>
+        <v>-0.01440724322771558</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2656464055365859</v>
+        <v>-0.2665955876120947</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2244163846092491</v>
+        <v>-0.2253742334907258</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2080744755190409</v>
+        <v>-0.2090470836689988</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1026212100736714</v>
+        <v>-0.1036159098582274</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.09601043222241401</v>
+        <v>-0.09700892034067721</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.0436616664367051</v>
+        <v>0.04261794355801385</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.07423336714973772</v>
+        <v>0.07318010683803067</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.01382431990142408</v>
+        <v>-0.0148713254406232</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2299111947343846</v>
+        <v>-0.2309068383891386</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.310066610376218</v>
+        <v>-0.3110414437939326</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2513705238944368</v>
+        <v>-0.2523688901397918</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3629395141987928</v>
+        <v>-0.3733691498969449</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3799</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.05249343832021225</v>
+        <v>-0.05373156451493344</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08243884130725831</v>
+        <v>0.0811262228585079</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2194184548968749</v>
+        <v>-0.2206619042576605</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2062442657658963</v>
+        <v>-0.2074887008993187</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2837712655880935</v>
+        <v>-0.2850088398463697</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2610667056761997</v>
+        <v>-0.2623037726185373</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2263604807616133</v>
+        <v>-0.2276093329055655</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1007305795112856</v>
+        <v>-0.1020242792909869</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.09464424967017493</v>
+        <v>-0.09594166626025924</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.08838193679304851</v>
+        <v>-0.08970202403632044</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.199454927680371</v>
+        <v>-0.200751369136789</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2556011340178941</v>
+        <v>-0.2568826395095556</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1494014148759391</v>
+        <v>-0.1358453685243362</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1892299641474224</v>
+        <v>-0.1996595998455746</v>
       </c>
     </row>
     <row r="12">
@@ -2529,514 +2529,514 @@
         <v>3683</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2299522806328511</v>
+        <v>-0.2174299909572284</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1249229909038618</v>
+        <v>0.1231323572909488</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3784055855408823</v>
+        <v>-0.3653984541232802</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2063511307054995</v>
+        <v>-0.208058343072878</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.310815199045912</v>
+        <v>-0.2977043946709728</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2303518346961297</v>
+        <v>-0.2173089384017644</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.08329492392993387</v>
+        <v>-0.08504072430205412</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.08849373850372899</v>
+        <v>0.0866853235886893</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.06963582236461008</v>
+        <v>0.06782963333861147</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1033806236546582</v>
+        <v>0.1015368290503176</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.07422092222142851</v>
+        <v>-0.06076362851121075</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1755966570834318</v>
+        <v>-0.1621443683633217</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.05281569919858242</v>
+        <v>-0.03925965284697952</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2375228219861043</v>
+        <v>-0.2479524576842564</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.09871</t>
+          <t>X &gt; -0.09869</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3511</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.05569298141348611</v>
+        <v>0.06821527108910885</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2099980354956585</v>
+        <v>0.2229078450717097</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1848706711009314</v>
+        <v>-0.1718635396833292</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.168545194431907</v>
+        <v>-0.1555660520334428</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5360749255963526</v>
+        <v>-0.5229641212214133</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1816691599114577</v>
+        <v>-0.1686262636170923</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.01841626266245555</v>
+        <v>0.03148251696293158</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2347987995118359</v>
+        <v>0.2479798088070737</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2307627412987756</v>
+        <v>0.2439614802535388</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2635768897940594</v>
+        <v>0.2769820174468904</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1442693074303421</v>
+        <v>0.1577266011405598</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.06472480883729048</v>
+        <v>0.07817709755740054</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.2425903915694079</v>
+        <v>0.2561464379210108</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1220468420456342</v>
+        <v>0.1116172063474821</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.07472</t>
+          <t>X &gt; -0.0747</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3315</v>
+        <v>3313</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.02541537511431358</v>
+        <v>0.06964237574395327</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3746260758755398</v>
+        <v>0.3902401643583531</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2615699308718789</v>
+        <v>-0.246004205606468</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1614827107832326</v>
+        <v>-0.1459631851693288</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5189084507422805</v>
+        <v>-0.5031479993576866</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2516324255454734</v>
+        <v>-0.2359580928738225</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.03470701762921635</v>
+        <v>-0.0188272206277702</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4030869591548978</v>
+        <v>0.4196278301221739</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.281755247934889</v>
+        <v>0.2982774272969522</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4572710885479836</v>
+        <v>0.4746188181086524</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1620200266738436</v>
+        <v>0.2095494135460143</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2567350090569818</v>
+        <v>0.2741116890525603</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4699645610080054</v>
+        <v>0.4878274219148224</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3576949430580498</v>
+        <v>0.3211694711754589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.05072</t>
+          <t>X &gt; -0.05071</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3054</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1260770694429425</v>
+        <v>0.1385993591185652</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8393233647956393</v>
+        <v>0.8522331743716904</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3462228310870685</v>
+        <v>0.3592299625046707</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.08017105660667312</v>
+        <v>-0.06719191420820891</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4548725598255388</v>
+        <v>-0.4417617554505995</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.157430622109878</v>
+        <v>-0.1443877258155126</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2162508538070966</v>
+        <v>0.2293171081075727</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4694341871801555</v>
+        <v>0.4826151964753933</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2119706467738851</v>
+        <v>0.2251693857286483</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4423955599777827</v>
+        <v>0.4558006876306138</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.02430930330508829</v>
+        <v>-0.01085200959487054</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1737935658936536</v>
+        <v>0.1872458546137636</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4411617447326392</v>
+        <v>0.4547177910842422</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1669799990783432</v>
+        <v>0.156550363380191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02673</t>
+          <t>X &gt; -0.02672</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2730</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6933748666032145</v>
+        <v>0.7058971562788372</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.389493561331264</v>
+        <v>1.402403370907315</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6649545250643456</v>
+        <v>0.6779616564819477</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7219475844117724</v>
+        <v>0.7349267268102366</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.183526369339603</v>
+        <v>0.1966371737145423</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3710781971651542</v>
+        <v>0.3841210934595196</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9823151758635689</v>
+        <v>0.9953814301640449</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.027952289902579</v>
+        <v>1.041133299197817</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.003582440350314</v>
+        <v>1.016781179305077</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.179098280963409</v>
+        <v>1.19250340861624</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.644674626975501</v>
+        <v>0.6581319206857188</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6424277476908955</v>
+        <v>0.6558800364110056</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6983636129364683</v>
+        <v>0.7119196592880712</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7649347620625733</v>
+        <v>0.7545051263644211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.002739</t>
+          <t>X &gt; -0.002725</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2396</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.429767022027079</v>
+        <v>1.442289311702702</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.238894577677186</v>
+        <v>2.251804387253237</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.219651914486271</v>
+        <v>2.232659045903873</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.224696365958543</v>
+        <v>2.237675508357007</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.602802696796225</v>
+        <v>1.615913501171164</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.816772180421736</v>
+        <v>1.829815076716102</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.775444139276338</v>
+        <v>2.788510393576814</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.475205648675143</v>
+        <v>2.488386657970381</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.49767821658299</v>
+        <v>2.510876955537753</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.649222480636858</v>
+        <v>2.662627608289689</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.152315567003754</v>
+        <v>2.165772860713972</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.019753816168887</v>
+        <v>2.033206104888997</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.309015064990263</v>
+        <v>2.322571111341865</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.266582807951025</v>
+        <v>2.256153172252873</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.02125</t>
+          <t>X &gt; 0.02127</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.11341165567039</v>
+        <v>2.152288602670282</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.57612651352138</v>
+        <v>2.616392084896027</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.615411207793102</v>
+        <v>2.607721086241376</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.504468006584865</v>
+        <v>2.496633488516999</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.821328991223261</v>
+        <v>1.813556290633656</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.408206529517798</v>
+        <v>2.400505609844039</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.38473668103471</v>
+        <v>3.377571312353922</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.062271082542644</v>
+        <v>3.055290313354831</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.097749729886637</v>
+        <v>3.090833253357147</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.453606213937334</v>
+        <v>3.447478163591001</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.911178022277745</v>
+        <v>2.904939167492969</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.60788631228116</v>
+        <v>2.601479482010454</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.959459969546572</v>
+        <v>2.953529400897814</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.63031010066512</v>
+        <v>2.600114471973768</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.04525</t>
+          <t>X &gt; 0.04526</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1791</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.777918463709625</v>
+        <v>1.790440753385248</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.734742394017282</v>
+        <v>2.747652203593333</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.563212604226941</v>
+        <v>2.576219735644543</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.470126820028192</v>
+        <v>2.483105962426656</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.32254870936697</v>
+        <v>2.335659513741909</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.899164293090443</v>
+        <v>2.912207189384809</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.707786243043181</v>
+        <v>3.720852497343657</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.910619594680433</v>
+        <v>3.923800603975671</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.96128916690126</v>
+        <v>3.974487905856023</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.395362753509289</v>
+        <v>4.40876788116212</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.855601053982333</v>
+        <v>3.869058347692551</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.666645294521508</v>
+        <v>3.680097583241619</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.083911621600052</v>
+        <v>4.097467667951655</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.831120391062278</v>
+        <v>3.820690755364126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.06924</t>
+          <t>X &gt; 0.06925</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.949428481683199</v>
+        <v>2.931803861211243</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.771931947826445</v>
+        <v>3.756341719432946</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.038996980242693</v>
+        <v>3.023275341443806</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.777769382627078</v>
+        <v>3.762431472853542</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.374574671949773</v>
+        <v>3.359459917051488</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.46917685307313</v>
+        <v>3.453856950746115</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.195802162170025</v>
+        <v>4.181054575241788</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.337138033165402</v>
+        <v>4.32291691927643</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4.54659115577283</v>
+        <v>4.532570757340935</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.048731014693509</v>
+        <v>5.103490932594298</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.641137933783639</v>
+        <v>4.628153779746825</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.405068082339348</v>
+        <v>4.391895937514867</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.728559245566188</v>
+        <v>4.715994069316473</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.302148055868159</v>
+        <v>4.265139733074804</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.09323</t>
+          <t>X &gt; 0.09324</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1245</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.00856971191854</v>
+        <v>3.021092001594162</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.449204934295643</v>
+        <v>4.462114743871695</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.652729801996252</v>
+        <v>3.665736933413854</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.58619578600937</v>
+        <v>4.599174928407834</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.208417141218327</v>
+        <v>4.221527945593266</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4.184573938371742</v>
+        <v>4.197616834666107</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.903053072505081</v>
+        <v>4.916119326805557</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.319403810269762</v>
+        <v>5.332584819565</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.900974205211959</v>
+        <v>5.914172944166722</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.737596008135839</v>
+        <v>6.75100113578867</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>6.05091497297488</v>
+        <v>6.064372266685098</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.165619415460888</v>
+        <v>6.179071704180998</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.950184081624407</v>
+        <v>6.96374012797601</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.477013847635639</v>
+        <v>6.466584211937487</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1040</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.891177064405412</v>
+        <v>2.903699354081034</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.741141912979614</v>
+        <v>4.754051722555666</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.250119360229178</v>
+        <v>4.26312649164678</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.053449415913597</v>
+        <v>5.066428558312062</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.611182046995275</v>
+        <v>4.624292851370214</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5.004777830864782</v>
+        <v>5.017820727159148</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.895168407118703</v>
+        <v>5.908349416413941</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.930322367090248</v>
+        <v>5.943521106045011</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.522504874370007</v>
+        <v>6.535910002022838</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.125443857744735</v>
+        <v>6.138901151454952</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>6.352134707397859</v>
+        <v>6.365586996117969</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7.566495481068351</v>
+        <v>7.580051527419954</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>7.046986044113858</v>
+        <v>7.036556408415706</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.823303761237995</v>
+        <v>2.835826050913617</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.057883994427577</v>
+        <v>5.070793804003628</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.663015287830987</v>
+        <v>4.676022419248589</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.150734483786898</v>
+        <v>6.163713626185363</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.707335893149121</v>
+        <v>4.720446697524061</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.552289143081978</v>
+        <v>4.565332039376344</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.580677597755404</v>
+        <v>4.59374385205588</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.697204606213717</v>
+        <v>5.710385615508955</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.409960376140013</v>
+        <v>5.423159115094776</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.369789942243308</v>
+        <v>6.383195069896139</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.82567010208863</v>
+        <v>5.839127395798847</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.19941977527116</v>
+        <v>6.21287206399127</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.249753399620374</v>
+        <v>7.263309445971977</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.707619528276751</v>
+        <v>6.697189892578599</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>746</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.600395459950889</v>
+        <v>2.612917749626511</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.669786994439711</v>
+        <v>3.682696804015762</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.21325608945169</v>
+        <v>4.226263220869292</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.818040053158391</v>
+        <v>5.831019195556856</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.475329293850294</v>
+        <v>4.488440098225233</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.37062645944799</v>
+        <v>4.383669355742356</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.419940999548366</v>
+        <v>4.433007253848842</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.159191917120758</v>
+        <v>5.172372926415996</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.232240288311111</v>
+        <v>5.245439027265874</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.856645934382378</v>
+        <v>5.870051062035209</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.517844352692144</v>
+        <v>5.531301646402362</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.222468796900849</v>
+        <v>6.235921085620959</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.276745017055141</v>
+        <v>7.290301063406744</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.856225062468155</v>
+        <v>6.845795426770003</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>605</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.721437712847873</v>
+        <v>1.733960002523496</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.093335174263785</v>
+        <v>2.106244983839836</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.855491261055626</v>
+        <v>2.868498392473228</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.465083236638336</v>
+        <v>5.4780623790368</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.934926484376078</v>
+        <v>3.948037288751017</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.736500653496698</v>
+        <v>3.749543549791063</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.312923961017816</v>
+        <v>4.325990215318292</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.168054611823081</v>
+        <v>5.181235621118319</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.107054725640779</v>
+        <v>5.120253464595542</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.413954334001282</v>
+        <v>5.427359461654113</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.209201009683703</v>
+        <v>5.222658303393921</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.574162679425825</v>
+        <v>5.587614968145935</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.1373791428611</v>
+        <v>7.150935189212703</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.560654194145641</v>
+        <v>6.550224558447489</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>473</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.064538514920187</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.497525064711603</v>
+        <v>1.510434874287654</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.273903715408878</v>
+        <v>4.28691084682648</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.941154733851469</v>
+        <v>6.954133876249934</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.711401594889239</v>
+        <v>4.724512399264178</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.374594061146134</v>
+        <v>4.387636957440499</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.501276834360112</v>
+        <v>4.514343088660588</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.091175888009907</v>
+        <v>5.104356897305145</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.818759511341341</v>
+        <v>4.831958250296104</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.448549759717217</v>
+        <v>5.461954887370048</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.82096345442713</v>
+        <v>4.834420748137347</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.278179592745069</v>
+        <v>5.291631881465179</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.972089886662744</v>
+        <v>6.985645933014347</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.376145256994</v>
+        <v>6.365715621295848</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>390</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.147587320815667</v>
+        <v>3.16010961049129</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.048834220671921</v>
+        <v>2.061744030247972</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.961657821767645</v>
+        <v>3.974664953185247</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.912423774887962</v>
+        <v>6.925402917286426</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.553489739302975</v>
+        <v>3.566600543677914</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.59452142060838</v>
+        <v>3.607564316902746</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.509787703336102</v>
+        <v>3.522853957636578</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.324655586605878</v>
+        <v>4.337836595901116</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.49442493119281</v>
+        <v>3.507623670147574</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.182761284626416</v>
+        <v>4.196166412279247</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.20877719107807</v>
+        <v>3.222234484788288</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.874187788760651</v>
+        <v>4.887743835112254</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.867498864626683</v>
+        <v>4.85706922892853</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>337</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.809232302935428</v>
+        <v>1.82175459261105</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7911305000601843</v>
+        <v>0.8040403096362354</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.770149033819685</v>
+        <v>2.783156165237287</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.274289406783268</v>
+        <v>5.287268549181732</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.658716856399522</v>
+        <v>2.671827660774461</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.956158794115183</v>
+        <v>2.969201690409548</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.277953266753883</v>
+        <v>2.291019521054359</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.294449393194931</v>
+        <v>3.307630402490169</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.233449507012629</v>
+        <v>3.246648245967393</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.757211562340792</v>
+        <v>4.770616689993624</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.662250522889686</v>
+        <v>3.675707816599903</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.399897775190603</v>
+        <v>3.413350063910713</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.463322689468249</v>
+        <v>4.476878735819852</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.41630811670003</v>
+        <v>4.405878481001878</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>288</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.367672790901139</v>
+        <v>2.380195080576762</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2855674887297894</v>
+        <v>-0.2726576791537383</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.097341582451399</v>
+        <v>2.110348713869001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.658150270614456</v>
+        <v>4.67112941301292</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.383617944431172</v>
+        <v>2.396728748806112</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.98661543770239</v>
+        <v>1.999658333996756</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.943548387096776</v>
+        <v>2.956614641397252</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.823587210537504</v>
+        <v>2.836768219832742</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.720920657688531</v>
+        <v>1.734119396643294</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.606906583771718</v>
+        <v>2.620311711424549</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.707708815009696</v>
+        <v>1.721166108719913</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.047647527910677</v>
+        <v>1.061099816630787</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.266003138130955</v>
+        <v>2.255573502432803</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>239</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.899867119120564</v>
+        <v>1.912389408796187</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.543523631679321</v>
+        <v>1.556433441255372</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7302448832417312</v>
+        <v>0.7432520146593333</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.789368308736265</v>
+        <v>3.802347451134729</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.995716968141082</v>
+        <v>2.008827772516021</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2011086966517226</v>
+        <v>0.214151592946088</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.9531950630614432</v>
+        <v>0.9662613173619192</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.4860116642799426</v>
+        <v>0.4991926735751804</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4118083055843584</v>
+        <v>-0.3986095666295952</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.0067033650892796</v>
+        <v>0.006701762563551483</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.6253633942751549</v>
+        <v>0.6388206879853726</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.432303657584434</v>
+        <v>-1.418851368864324</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.434148226688336</v>
+        <v>-1.420592180336733</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.021246978094062</v>
+        <v>-2.031676613792214</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>193</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.428841472536135</v>
+        <v>2.441363762211758</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2190015704799322</v>
+        <v>-0.206091760903881</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.9405338680011965</v>
+        <v>0.9535409994187987</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.143325860712331</v>
+        <v>3.156305003110795</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.5039036445152831</v>
+        <v>-0.4907928401403439</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.351539427006877</v>
+        <v>-4.338496530712511</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.400003714227338</v>
+        <v>-3.386937459926862</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.867187113008839</v>
+        <v>-3.854006103713601</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.446321714217049</v>
+        <v>-4.433122975262286</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.742042754167265</v>
+        <v>-3.728637626514434</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.392391933407119</v>
+        <v>-2.378934639696901</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.876143491087596</v>
+        <v>-2.862691202367486</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.814532817058407</v>
+        <v>-3.800976770706804</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-5.119215629859831</v>
+        <v>-5.129645265557983</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>152</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.453930100842655</v>
+        <v>1.466452390518278</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.8155382489636978</v>
+        <v>-0.8026284393876466</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.7632772549660274</v>
+        <v>0.7762843863836295</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.209319861257725</v>
+        <v>2.22229900365619</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.618575038024957</v>
+        <v>-1.605464233650018</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.242185731888256</v>
+        <v>-7.22914283559389</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-4.037445764950007</v>
+        <v>-4.024379510649531</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.539313260440125</v>
+        <v>-6.526114521485361</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.389438445468052</v>
+        <v>-7.376033317815221</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-4.962612822417206</v>
+        <v>-4.949155528706989</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-7.072447154266712</v>
+        <v>-7.082876789964864</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>120</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.685750636132312</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.438345266507561</v>
+        <v>-2.42543545693151</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.869627507163322</v>
+        <v>-1.856648364764858</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.074715388902163</v>
+        <v>-4.061604584527224</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-8.777273451186502</v>
+        <v>-8.764230554892137</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.329190567240282</v>
+        <v>-4.316009557945044</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.740315638450504</v>
+        <v>-7.726910510797673</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.611735629434747</v>
+        <v>-4.59827833572453</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-4.577352472089316</v>
+        <v>-4.563900183369206</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.164273749700889</v>
+        <v>-4.150717703349287</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.914552417424602</v>
+        <v>-3.924982053122754</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.408522464103754</v>
+        <v>2.421044753779377</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.519488482908081</v>
+        <v>-3.506481351490478</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-3.389235350300581</v>
+        <v>-3.376256207902117</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.868833035960982</v>
+        <v>-6.855722231586043</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.4929597256963</v>
+        <v>-10.47991682940194</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.6561248155176</v>
+        <v>-6.643058561217124</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-7.123308214299101</v>
+        <v>-7.110127205003863</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7.184308100481402</v>
+        <v>-7.171109361526639</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-8.03443328550933</v>
+        <v>-8.021028157856499</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.317617982375921</v>
+        <v>-4.304160688665704</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.263626981893246</v>
+        <v>-5.250174693173136</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.703489435975392</v>
+        <v>-4.689933389623789</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-4.453768103699105</v>
+        <v>-4.464197739397257</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.133067703886418</v>
+        <v>4.145589993562041</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.502602294620019</v>
+        <v>-3.489692485043967</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-6.30710955543347</v>
+        <v>-6.294102424015868</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.176856422825971</v>
+        <v>-6.163877280427506</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-12.73937402344031</v>
+        <v>-12.72626321906537</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-13.64675136283309</v>
+        <v>-13.63370846653872</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-8.912207971671627</v>
+        <v>-8.899141717371151</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-10.58421064756156</v>
+        <v>-10.57102963826632</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.440391256635429</v>
+        <v>-9.427192517680666</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-10.29051644166336</v>
+        <v>-10.27711131401053</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-6.88081193465564</v>
+        <v>-6.867354640945422</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.641609500201774</v>
+        <v>-5.628157211481664</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-7.26668338825511</v>
+        <v>-7.253127341903507</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-5.812142778870388</v>
+        <v>-5.82257241456854</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-50 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-50 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,157 +3904,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.2667</t>
+          <t>X &lt; -0.2666</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.337886980994838</v>
+        <v>5.350409270670461</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.521494090922161</v>
+        <v>2.534403900498212</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.331444661433991</v>
+        <v>3.344451792851594</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.280974902475236</v>
+        <v>8.293954044873701</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.742553687403067</v>
+        <v>7.755664491778006</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.835176348010286</v>
+        <v>6.848219244304651</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.54562335362958</v>
+        <v>5.558689607930056</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.9456564306940933</v>
+        <v>-0.9324754213988555</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.006656316876395</v>
+        <v>-0.9934575779216317</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.5528570523125538</v>
+        <v>0.5662621799653849</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.552923005103395</v>
+        <v>1.566380298813613</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.611402547990991</v>
+        <v>7.624854836711101</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.371870828612366</v>
+        <v>2.385426874963969</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.621592160888653</v>
+        <v>2.611162525190501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.2427</t>
+          <t>X &lt; -0.2426</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.961107134335478</v>
+        <v>2.973629424011101</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.863755723865538</v>
+        <v>1.87676285528314</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.994008856473037</v>
+        <v>2.006987998871502</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.662120488207442</v>
+        <v>2.675163384501808</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.48647768002607</v>
+        <v>3.499543934326546</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.110203372153663</v>
+        <v>2.123384381448901</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.587160150392272</v>
+        <v>-1.573961411437509</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.10816921003434</v>
+        <v>2.121574337687171</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.903415885716761</v>
+        <v>1.916873179426979</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.574162679425825</v>
+        <v>5.587614968145935</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.426635341208204</v>
+        <v>2.440191387559807</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.494538491666312</v>
+        <v>4.484108855968159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.2187</t>
+          <t>X &lt; -0.2186</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>144</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.685750636132312</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.021678599840897</v>
+        <v>-2.008768790264845</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.185928048392235</v>
+        <v>1.198907190790699</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.036395722208951</v>
+        <v>2.04950652658389</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.832829006742053</v>
+        <v>-1.819786110447687</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1657706093190043</v>
+        <v>0.1788368636194804</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.384746122795832</v>
+        <v>-2.371565113500594</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.834634897867026</v>
+        <v>-3.821436158912263</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1763510282161604</v>
+        <v>0.1897561558689915</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.783758639021791</v>
+        <v>2.797210927741901</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.613225360353177</v>
+        <v>2.602795724655024</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>188</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.357625509577254</v>
+        <v>3.370147799252877</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.746051896612997</v>
+        <v>1.758961706189048</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.010757658101518</v>
+        <v>4.02376478951912</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.077181003474983</v>
+        <v>3.090160145873448</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.134504469253876</v>
+        <v>4.147615273628816</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.772371938884419</v>
+        <v>1.785414835178784</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.28338290246321</v>
+        <v>3.296449156763686</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.220454822830639</v>
+        <v>1.233635832125877</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.6275400430313169</v>
+        <v>0.6407387819860801</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.968904219705529</v>
+        <v>2.98230934735836</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.359895576239012</v>
+        <v>4.37335286994923</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.053853201669547</v>
+        <v>7.067305490389657</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.569768803490604</v>
+        <v>5.583324849842207</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.883319923000933</v>
+        <v>6.872890287302781</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.01636560135865</v>
+        <v>2.028887891034273</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.189105713884594</v>
+        <v>1.202015523460645</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.931491909248791</v>
+        <v>3.944499040666393</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.669588179111194</v>
+        <v>3.682567321509659</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.915480689529218</v>
+        <v>3.928591493904158</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.252138313519382</v>
+        <v>2.265181209813747</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.951718321737296</v>
+        <v>2.964784576037772</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5237506092303121</v>
+        <v>0.5369316185255499</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.8549075857931072</v>
+        <v>0.8681063247478704</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.18125298900047</v>
+        <v>1.194658116653301</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.113754566643678</v>
+        <v>4.127211860353896</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.932451449479309</v>
+        <v>4.945903738199419</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.512196838534408</v>
+        <v>4.52575288488601</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.79017199202422</v>
+        <v>5.927959123347833</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.422224330392439</v>
+        <v>1.434746620068061</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1893492825718184</v>
+        <v>-0.1764394729957672</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.427830203602667</v>
+        <v>2.440837335020269</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.558083336210167</v>
+        <v>2.571062478608631</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.826891036800653</v>
+        <v>3.840001841175592</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.5219233359621</v>
+        <v>3.534966232256465</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.738394437966932</v>
+        <v>3.751460692267408</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.066391762076996</v>
+        <v>2.079572771372234</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.607801514448902</v>
+        <v>2.621000253403665</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.757676329420974</v>
+        <v>1.771081457073805</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.757742282211836</v>
+        <v>2.771199575922054</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.093330258834378</v>
+        <v>3.106782547554488</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.248112957247749</v>
+        <v>2.084222055686858</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.373326370454187</v>
+        <v>2.487404653825884</v>
       </c>
     </row>
     <row r="12">
@@ -4220,517 +4220,517 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.473449097008569</v>
+        <v>2.364898947439222</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4626278272139714</v>
+        <v>-0.4497180176379203</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.022243254034485</v>
+        <v>2.908269979505505</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.825062758323405</v>
+        <v>1.838041900721869</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.963348173551651</v>
+        <v>2.848424913997853</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.278282104369055</v>
+        <v>2.165185557450812</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.526881720430104</v>
+        <v>1.53994797473058</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.05141278946249628</v>
+        <v>-0.03823178016725848</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5542539910218665</v>
+        <v>0.5674527299766297</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.295871194006061</v>
+        <v>-0.2824660663532299</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9599050535645119</v>
+        <v>0.8461661087199133</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.568480861244012</v>
+        <v>1.453174798071025</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.8301334091358044</v>
+        <v>0.715353725222144</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.10562695477271</v>
+        <v>2.187993338376124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.09871</t>
+          <t>X &lt; -0.09869</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1214586686965262</v>
+        <v>0.05072953908589994</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7716785998408966</v>
+        <v>-0.8432907131386003</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9850160215964223</v>
+        <v>0.9099518884721789</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.044385231690178</v>
+        <v>0.9692657846786972</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.305667386217458</v>
+        <v>3.226081190419706</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.299936346470588</v>
+        <v>1.223807722619831</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5046594982078929</v>
+        <v>0.4295468387703494</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8356008236505374</v>
+        <v>-0.9093428912783708</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.4883712987944335</v>
+        <v>-0.5628891503652582</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.089726142201854</v>
+        <v>-1.164577712509818</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5618161447326528</v>
+        <v>-0.6379353560889527</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2762772032721159</v>
+        <v>-0.3529501028539102</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.09076809541979</v>
+        <v>-1.166846735607351</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5893096989779991</v>
+        <v>-0.5283746217818788</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.07472</t>
+          <t>X &lt; -0.0747</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2272388261019955</v>
+        <v>0.04920445139335783</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.199442925910311</v>
+        <v>-1.257361472210967</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.015270875380693</v>
+        <v>0.9479091003424358</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.7274598714774498</v>
+        <v>0.6614894828772222</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.321598908384189</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.228809273874333</v>
+        <v>1.160011869350299</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6030760633723204</v>
+        <v>0.536172354450116</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.260084876183363</v>
+        <v>-1.321882380950299</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5226690859012066</v>
+        <v>-0.5874540015724321</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.550421587920759</v>
+        <v>-1.614446036579245</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4644488077293261</v>
+        <v>-0.6551889048302186</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9744112956187294</v>
+        <v>-1.041311660780686</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.694948596326654</v>
+        <v>-1.760742153227035</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.377697380569565</v>
+        <v>-1.223023668789828</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.05072</t>
+          <t>X &lt; -0.05071</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1037324378570332</v>
+        <v>-0.139318234391105</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.127091050009561</v>
+        <v>-2.161955064774652</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.000801450083898</v>
+        <v>-1.037011502833444</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2847503730210121</v>
+        <v>0.2474032006126734</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.457264930901033</v>
+        <v>1.418426137438992</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6063830585087899</v>
+        <v>0.5684877722911352</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2591112966165099</v>
+        <v>-0.2963093352109283</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.045965158667968</v>
+        <v>-1.082799453200742</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1309311941633169</v>
+        <v>-0.1686969256919966</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.022675848521558</v>
+        <v>-1.060243844131001</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2151041974050756</v>
+        <v>0.1762042098423535</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.4408622213929405</v>
+        <v>-0.4791753843586974</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.088065571262234</v>
+        <v>-1.126112318019672</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-0.3840898598142104</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02673</t>
+          <t>X &lt; -0.02672</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.14782925505417</v>
+        <v>-1.171644976040362</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.510398184060129</v>
+        <v>-2.534028469207243</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.308391278068697</v>
+        <v>-1.333081871216436</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.353303873380497</v>
+        <v>-1.377924960509532</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2205487222354918</v>
+        <v>-0.2462509057952644</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5949706793314817</v>
+        <v>-0.6202911609527391</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.637019022417995</v>
+        <v>-1.661663017925186</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.781740982424147</v>
+        <v>-1.806526390567143</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.591045154277282</v>
+        <v>-1.61601899797909</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.117839991028312</v>
+        <v>-2.14286492675209</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.142881611365326</v>
+        <v>-1.16872262177823</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.211899224409088</v>
+        <v>-1.237699517653567</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.235702321129459</v>
+        <v>-1.261709851814665</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.44671825016227</v>
+        <v>-1.424982053122747</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.002739</t>
+          <t>X &lt; -0.002725</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.80615309684228</v>
+        <v>-1.82264470826761</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.930226832887698</v>
+        <v>-2.946626751318689</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.066394401238711</v>
+        <v>-3.082862047035164</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.021377363732462</v>
+        <v>-3.037841025315309</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.09518993922746</v>
+        <v>-2.112379111205364</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.399234010252172</v>
+        <v>-2.416163199362089</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.603386478803607</v>
+        <v>-3.619666550765622</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.236129420987645</v>
+        <v>-3.252791167140444</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.152177411612065</v>
+        <v>-3.168921942568254</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.511760658600195</v>
+        <v>-3.528598274510756</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.879784784580679</v>
+        <v>-2.897069354722809</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.75698743846781</v>
+        <v>-2.774345651879194</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.088725883495577</v>
+        <v>-3.10604911545304</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.096606658624836</v>
+        <v>-3.080114694414561</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.02125</t>
+          <t>X &lt; 0.02127</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.985946778402337</v>
+        <v>-2.02220043420408</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.460911352903445</v>
+        <v>-2.497899225047462</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.637277833771783</v>
+        <v>-2.62607118839189</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.481921795643473</v>
+        <v>-2.470768287395416</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.736135889305714</v>
+        <v>-1.726094182979089</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.333475001574094</v>
+        <v>-2.322636492291295</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.216911030148871</v>
+        <v>-3.205276668799137</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.931680059642481</v>
+        <v>-2.920660720735732</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.870297197721463</v>
+        <v>-2.859379822401245</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.35520236984209</v>
+        <v>-3.344433950823543</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.854410066863927</v>
+        <v>-2.84427542451639</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.599704269951324</v>
+        <v>-2.589790151006753</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.896650998120919</v>
+        <v>-2.886754614471187</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.620778098358457</v>
+        <v>-2.586303724648509</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.04525</t>
+          <t>X &lt; 0.04526</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.238653122421795</v>
+        <v>-1.247922833255444</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.977352358706142</v>
+        <v>-1.986615096801074</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.966887876893004</v>
+        <v>-1.976235210480887</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.856850675817491</v>
+        <v>-1.866226908826164</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.691176118912097</v>
+        <v>-1.700730081403989</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.138313519387687</v>
+        <v>-2.147627799601693</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.669754147847549</v>
+        <v>-2.678864187815584</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.858769634362012</v>
+        <v>-2.867892997888177</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.81208545982463</v>
+        <v>-2.821246549507634</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.255544787326116</v>
+        <v>-3.26468259786553</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.882417674144989</v>
+        <v>-2.891759690691799</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.782480677217528</v>
+        <v>-2.791865440381876</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.051618768939882</v>
+        <v>-3.060974113605695</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.907281245482771</v>
+        <v>-2.897833699125322</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.06924</t>
+          <t>X &lt; 0.06925</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2650</v>
+        <v>2652</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.535871666060523</v>
+        <v>-1.524068000515591</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.001330490649813</v>
+        <v>-1.99000002149608</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.700181278628392</v>
+        <v>-1.689276812896971</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.076394424456552</v>
+        <v>-2.065138222015051</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.805378545477311</v>
+        <v>-1.794599699145785</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.864180900396427</v>
+        <v>-1.85320298596983</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.192517769387145</v>
+        <v>-2.181334044407762</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.301078117441079</v>
+        <v>-2.290050189999214</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.342167854552521</v>
+        <v>-2.33113799473378</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.720220185046841</v>
+        <v>-2.746990832082815</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.527931131382239</v>
+        <v>-2.517299051355415</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.435572683250712</v>
+        <v>-2.424990361716361</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.571478578067541</v>
+        <v>-2.56100794081631</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.376816568368</v>
+        <v>-2.352583863077506</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.09323</t>
+          <t>X &lt; 0.09324</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.19899579345816</v>
+        <v>-1.20417344944395</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.826006408312352</v>
+        <v>-1.831142510205012</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.581055078458213</v>
+        <v>-1.586321022165372</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.950829995069341</v>
+        <v>-1.955957518478158</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.745241947261412</v>
+        <v>-1.750501152138369</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.740620615778475</v>
+        <v>-1.745852861609499</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.980017084289521</v>
+        <v>-1.985178811806982</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.186745353860807</v>
+        <v>-2.19188872317045</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.367864389040442</v>
+        <v>-2.372954805586616</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.818801326354482</v>
+        <v>-2.823829860053472</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.554813795928226</v>
+        <v>-2.559958852806716</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.640415535152385</v>
+        <v>-2.645530480101684</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.938103905680087</v>
+        <v>-2.943163995795572</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.773775718395477</v>
+        <v>-2.768136299223272</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8815750062190091</v>
+        <v>-0.885685608362266</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.509075138591847</v>
+        <v>-1.513120821212631</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.435364510738566</v>
+        <v>-1.4394694451478</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.675209953113637</v>
+        <v>-1.679229009926154</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.486486423978548</v>
+        <v>-1.490613942384591</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.62384540253727</v>
+        <v>-1.627906044455287</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.659164791197796</v>
+        <v>-1.663223553271422</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.883040863416902</v>
+        <v>-1.887068989469583</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.829858628384869</v>
+        <v>-1.833911477526513</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.11309287737712</v>
+        <v>-2.117128136309418</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.009320795454585</v>
+        <v>-2.013409276558676</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.119140458717162</v>
+        <v>-2.123192981989305</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.489516468147492</v>
+        <v>-2.493487033663101</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.35174892114749</v>
+        <v>-2.347312150210136</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6825113711614819</v>
+        <v>-0.6858868804883258</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.295678190466226</v>
+        <v>-1.298977507269143</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.275064914955102</v>
+        <v>-1.278399452473579</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.650733497946732</v>
+        <v>-1.653945662062164</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.220279822419876</v>
+        <v>-1.223662956263013</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.183001497092839</v>
+        <v>-1.186377655896024</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.128304831435408</v>
+        <v>-1.131705541681612</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.455972070367515</v>
+        <v>-1.459305990909364</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.315831479063597</v>
+        <v>-1.319214620240395</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.656905358364327</v>
+        <v>-1.660243844131003</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.537022985756593</v>
+        <v>-1.540414377583566</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.670566721139721</v>
+        <v>-1.673916603730461</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.919973071943652</v>
+        <v>-1.923276988843597</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.807464589997785</v>
+        <v>-1.803909964398166</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4910826076069128</v>
+        <v>-0.4938686357742768</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7324051585055997</v>
+        <v>-0.735211664234221</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9347657311084774</v>
+        <v>-0.9375362476757516</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.260284742648146</v>
+        <v>-1.262953609314067</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.9280958920468123</v>
+        <v>-0.9308942986445246</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9096336202615021</v>
+        <v>-0.9124223787915042</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8605322422050889</v>
+        <v>-0.8633417791931919</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.046265417245195</v>
+        <v>-1.049047906027631</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.002744565976684</v>
+        <v>-1.005544876659215</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.21684353924767</v>
+        <v>-1.219629912607992</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.16912881707011</v>
+        <v>-1.171942345172418</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.35480200433944</v>
+        <v>-1.357560352693888</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.551980605492851</v>
+        <v>-1.554705886510291</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.492885258098568</v>
+        <v>-1.48999387345372</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.217498258010373</v>
+        <v>-0.2197515308169997</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2871386300068153</v>
+        <v>-0.2894445041466724</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4970517854568186</v>
+        <v>-0.4993169472672534</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9174486729810951</v>
+        <v>-0.9195903732514239</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6199083316326011</v>
+        <v>-0.6221591968645157</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5902217335572004</v>
+        <v>-0.5924690679593994</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6313359704978581</v>
+        <v>-0.6335766257475797</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.7999176682789937</v>
+        <v>-0.802132469301597</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7321664617346642</v>
+        <v>-0.7344043679144718</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.858229470650052</v>
+        <v>-0.8604705372452059</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.8488587746951168</v>
+        <v>-0.8511128028447175</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9405591274116887</v>
+        <v>-0.9427868670475092</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.17491204757323</v>
+        <v>-1.177093199662387</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.108082496879767</v>
+        <v>-1.105833116952539</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1903584619379686</v>
+        <v>-0.1920876926596904</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.1246411589103218</v>
+        <v>-0.1264439061002207</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5593297807580058</v>
+        <v>-0.5610283611340208</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8780835900874848</v>
+        <v>-0.8796917244594269</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5560705503391716</v>
+        <v>-0.5577857083679163</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5167203216377274</v>
+        <v>-0.5184370123728073</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4774862839378855</v>
+        <v>-0.4792174789326822</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5748668825506726</v>
+        <v>-0.5765883185237968</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4843814759118743</v>
+        <v>-0.4861306185275254</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6364905018384803</v>
+        <v>-0.6382280014650661</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5801240780090424</v>
+        <v>-0.5818848931015808</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6672012054591008</v>
+        <v>-0.6689379896915213</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8534998913470417</v>
+        <v>-0.8552010275701747</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8073314108600442</v>
+        <v>-0.8056219218676333</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2546323500607244</v>
+        <v>-0.2560292732734979</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.1460676516493109</v>
+        <v>-0.1475392238113926</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4198806397708239</v>
+        <v>-0.4212909970229077</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.701982801908585</v>
+        <v>-0.7033150314315293</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3189345279985574</v>
+        <v>-0.3203847036701077</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3271800431267167</v>
+        <v>-0.3286204517260032</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2639470154066288</v>
+        <v>-0.2654074206968602</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3694664906937675</v>
+        <v>-0.3709125655976422</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2288656670977858</v>
+        <v>-0.2303517500708381</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3696682076908644</v>
+        <v>-0.3711412800284393</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2922986082339705</v>
+        <v>-0.2937988629308776</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.376604009111503</v>
+        <v>-0.3780815480583257</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4610651935511569</v>
+        <v>-0.462532726070485</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.4905085554294146</v>
+        <v>-0.4891531761174122</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.08870770260156746</v>
+        <v>-0.08995439101779823</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.004065560934485291</v>
+        <v>-0.005374134110667228</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.253233256126336</v>
+        <v>-0.2544865472596385</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4506375019029321</v>
+        <v>-0.4518363742310711</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.185607259462536</v>
+        <v>-0.186889522279273</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2158699424145709</v>
+        <v>-0.2171376845948387</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1020264717842068</v>
+        <v>-0.1033268790705861</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2125502302207991</v>
+        <v>-0.2138335467140138</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.15373184574986</v>
+        <v>-0.1550327887174134</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3571052415414755</v>
+        <v>-0.3583739468436704</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2836723883280285</v>
+        <v>-0.2849660772067963</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2872452853031646</v>
+        <v>-0.2885378645286352</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3500106334340813</v>
+        <v>-0.3512975662907749</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3755228815596183</v>
+        <v>-0.3743624907710554</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3841</v>
+        <v>3842</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1063080659287081</v>
+        <v>-0.1073751745032183</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.08652712729812606</v>
+        <v>0.08537582139403099</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.164470463239148</v>
+        <v>-0.1655654367207333</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3317152765738669</v>
+        <v>-0.332764667983966</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1288279430147057</v>
+        <v>-0.1299418129527368</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1029424561228467</v>
+        <v>-0.1040573947189714</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1215359279875372</v>
+        <v>-0.1226483706405048</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1326304771267672</v>
+        <v>-0.1337503756858567</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.00268526160601823</v>
+        <v>0.001528344452559338</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1308661369333848</v>
+        <v>-0.1320067146458257</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.0869350744573012</v>
+        <v>-0.08809194647442808</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.06395148327849398</v>
+        <v>-0.06511419654992778</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.0791618288263507</v>
+        <v>-0.08032998542058323</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1531621544722412</v>
+        <v>-0.1522074565584646</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3890</v>
+        <v>3891</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0466025528515317</v>
+        <v>-0.04751439119009859</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.03017851441461517</v>
+        <v>-0.03112338929123837</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.05230309555139456</v>
+        <v>-0.0532497256776665</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2157813533171691</v>
+        <v>-0.2166842529986468</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.07347575480795143</v>
+        <v>-0.07442509734772784</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.03280009080084767</v>
+        <v>0.03182826360833246</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.03907058365824412</v>
+        <v>0.03809517272386387</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.04794837868716684</v>
+        <v>0.04696195860615404</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1551668422556389</v>
+        <v>0.1541513382358133</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.06399869128755142</v>
+        <v>0.06299107242868729</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.0021011716612378</v>
+        <v>0.001105331455740099</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.102332351480392</v>
+        <v>0.1013108792217636</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1334646208979251</v>
+        <v>0.1324272092920253</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1407175054545817</v>
+        <v>0.1414533105369742</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.04978169828036982</v>
+        <v>-0.05053628369891072</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.07431937381665676</v>
+        <v>0.07350942362896262</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.05346564103760443</v>
+        <v>-0.05424939487804181</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1374937007771067</v>
+        <v>-0.1382546480179627</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.07293987092039345</v>
+        <v>0.07211732795799719</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2575473736951821</v>
+        <v>0.2566819926363877</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.262813188291581</v>
+        <v>0.2619448194454819</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2661924870468937</v>
+        <v>0.2653159978923156</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3461285857383842</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.2461479825308786</v>
+        <v>0.2452623725652572</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1572412682550137</v>
+        <v>0.1563747945631135</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1551682660180091</v>
+        <v>0.1543024061205145</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2318400425266987</v>
+        <v>0.2309481168640133</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.267358151681087</v>
+        <v>0.2679313327040163</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3977</v>
+        <v>3978</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.01282734395042695</v>
+        <v>0.01219346583247471</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.09403544712158407</v>
+        <v>0.09336153554968973</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.03649046925928445</v>
+        <v>-0.03713673221884761</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.06814769778284102</v>
+        <v>-0.06878477399254734</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1095127428924627</v>
+        <v>0.1088243093779724</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.3203844325441523</v>
+        <v>0.3196463475999209</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2494386146737497</v>
+        <v>0.2487169695723495</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.2730774049749627</v>
+        <v>0.272343855709579</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3766771173123971</v>
+        <v>0.3759164786864204</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3443364590124389</v>
+        <v>0.3435733331668374</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2291353923407939</v>
+        <v>0.2283983786688353</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2525880489796251</v>
+        <v>0.2518452102656354</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2990243900678351</v>
+        <v>0.2982644529713951</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.286478510410447</v>
+        <v>0.2869334823221905</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4009</v>
+        <v>4010</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.01775014324104518</v>
+        <v>0.01721968907787641</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.13522681340622</v>
+        <v>0.1346507356758124</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.02748254430878205</v>
+        <v>0.02692902832919941</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.07177582699940643</v>
+        <v>0.07121233175255526</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1691040901089593</v>
+        <v>0.1685107011989118</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3059976466477039</v>
+        <v>0.305372896244414</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2349383826700375</v>
+        <v>0.2343301836759011</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2048484531001193</v>
+        <v>0.2042427660921433</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.282206158435919</v>
+        <v>0.2815803071179062</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2931589026243344</v>
+        <v>0.2925214772441791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1772308045964905</v>
+        <v>0.1766199116382055</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1508948477810321</v>
+        <v>0.1502905776809698</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1686439560347779</v>
+        <v>0.1680307384358102</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1332151056484889</v>
+        <v>0.1336214381490635</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4027</v>
+        <v>4028</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.006561679790024755</v>
+        <v>0.006092135761115003</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1658471903712027</v>
+        <v>0.1653236189760818</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.08159533843620892</v>
+        <v>0.08108885856928794</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1015144299186659</v>
+        <v>0.1010039383554968</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2207917138398301</v>
+        <v>0.2202466251169071</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3088479862360529</v>
+        <v>0.3082834854117991</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2625177034632173</v>
+        <v>0.2619636707239792</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.2552792236515273</v>
+        <v>0.254722552449941</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3072301814980563</v>
+        <v>0.3066598269818854</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2647286020191828</v>
+        <v>0.2641609177737578</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1483967113427553</v>
+        <v>0.147855791456486</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1471449218049514</v>
+        <v>0.1466043658450147</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1629357835662404</v>
+        <v>0.1623872854816923</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.128780088162685</v>
+        <v>0.1291390988136882</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01745901496237678</v>
+        <v>-0.01786184334223861</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1335292201032416</v>
+        <v>0.1330764918243403</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1217609673280151</v>
+        <v>0.1213078617798473</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1422068123633053</v>
+        <v>0.141749466144681</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.3077342617349146</v>
+        <v>0.3072317073859949</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3227923274683278</v>
+        <v>0.3222881462998117</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2762854542898054</v>
+        <v>0.2757918600564651</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2915728417758459</v>
+        <v>0.291071616493646</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.3183177338562757</v>
+        <v>0.3178092068878939</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2720300405618445</v>
+        <v>0.2715260892187885</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.17998249026558</v>
+        <v>0.1794994420532419</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1294986478052778</v>
+        <v>0.1290281116830627</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1926573103435913</v>
+        <v>0.1921676721447838</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1351262775828062</v>
+        <v>0.1354330691900714</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_50.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_50.xlsx
@@ -568,989 +568,989 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.2546</t>
+          <t>X ≈ -0.2544</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.318938578775445</v>
+        <v>-2.502134465277116</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.926234191469952</v>
+        <v>-7.915881831174474</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.628038012552594</v>
+        <v>-4.475052093007186</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-17.27701684700544</v>
+        <v>-19.69331257309766</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.036538369158244</v>
+        <v>-4.835872500497175</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.13314690737986</v>
+        <v>-12.24183444424195</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.825537500642483</v>
+        <v>-4.626285935101983</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.50029898132983</v>
+        <v>10.269354762832</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.354120986996605</v>
+        <v>-5.130541252295835</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.895906633346286</v>
+        <v>5.572070693522555</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.992086326725016</v>
+        <v>1.526129422842551</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6747465667879737</v>
+        <v>-2.259673195416447</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.607891468284116</v>
+        <v>1.189979119433715</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.24168461354223</v>
+        <v>9.131632091059295</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.2306</t>
+          <t>X ≈ -0.2304</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>34</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.472895800829747</v>
+        <v>-2.502015103288755</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.944367366865237</v>
+        <v>-9.945633421922942</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.541604704428472</v>
+        <v>-1.54176844997825</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.412027346140952</v>
+        <v>-1.412529746701118</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-7.818668903260992</v>
+        <v>-7.770283679501951</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-16.32955523935048</v>
+        <v>-16.30573726121505</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-10.54610908251234</v>
+        <v>-10.49823551249401</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-16.88860119222288</v>
+        <v>-16.83950035124383</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.07856970166874</v>
+        <v>-11.00544707556699</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.054165028801194</v>
+        <v>-5.954937661587167</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.260243407830814</v>
+        <v>-6.160426158242011</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.227511936913409</v>
+        <v>-6.10388783203237</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.7681778166978148</v>
+        <v>-0.6195274251639873</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.483805582533186</v>
+        <v>-3.311806822967853</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.2067</t>
+          <t>X ≈ -0.2065</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.853546708239932</v>
+        <v>8.824532070119815</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14.04736490609584</v>
+        <v>14.04629825693745</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.65670767292125</v>
+        <v>13.65666118644035</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.256165083575254</v>
+        <v>9.255737455978561</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.98900377670402</v>
+        <v>11.03750409572215</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>13.55696364530733</v>
+        <v>13.58094551674785</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13.47577164149988</v>
+        <v>13.52375996452156</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.01291420096678</v>
+        <v>13.0621372069126</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>15.22524431463195</v>
+        <v>15.29845623796675</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>12.10934268035196</v>
+        <v>12.20861858395259</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>18.72083814460964</v>
+        <v>18.82070620855218</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.03144576905036</v>
+        <v>21.1551067409269</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>18.34462443732961</v>
+        <v>18.49328753464614</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>20.84774521960451</v>
+        <v>21.01974397917117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1827</t>
+          <t>X ≈ -0.1825</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>67</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.729153429793747</v>
+        <v>-1.758260716006362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3597076970814399</v>
+        <v>-0.3608934047330337</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.710982436414284</v>
+        <v>3.710862393696999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.330749490347266</v>
+        <v>5.33029707102245</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.305992102399316</v>
+        <v>3.354442761387986</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.603867270348047</v>
+        <v>3.627794001295442</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.030365980483694</v>
+        <v>2.078297141104457</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.415779824184057</v>
+        <v>-1.366619078095106</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.504277670403802</v>
+        <v>1.57743979019488</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.817579215544477</v>
+        <v>-3.718350849550582</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.433758596235087</v>
+        <v>3.533593195545237</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.00633349196162</v>
+        <v>-0.8827048499745942</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.557778325398395</v>
+        <v>1.706428785383288</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.276510484189998</v>
+        <v>1.955971930324509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.1587</t>
+          <t>X ≈ -0.1585</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5375453405354165</v>
+        <v>0.05511600637356651</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.789823528248455</v>
+        <v>-4.134364731327899</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.562675364763074</v>
+        <v>-3.235350264474903</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.119415527105879</v>
+        <v>-0.5140234366441163</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.588041228407711</v>
+        <v>2.879139274277222</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.828689229962571</v>
+        <v>8.339855259664901</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.431293281422739</v>
+        <v>6.984009267222056</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.272825898865413</v>
+        <v>7.809979423722879</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.527043475264414</v>
+        <v>9.071601936693106</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.725678989889012</v>
+        <v>4.348150614082378</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.738283518516809</v>
+        <v>-1.618495181434831</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.01826904216724</v>
+        <v>-2.858783849854241</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.07701176668111</v>
+        <v>-5.851210473705926</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-9.056561000491179</v>
+        <v>-9.499736540309343</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.1347</t>
+          <t>X ≈ -0.1345</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.143693475028208</v>
+        <v>4.310767971186593</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.252568545371446</v>
+        <v>-3.099164280571074</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.374723553975542</v>
+        <v>4.689575307055044</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1894025618888264</v>
+        <v>-0.08646095090006867</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1180750258346634</v>
+        <v>0.2190349649202048</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.690889759000648</v>
+        <v>-1.505946337049707</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.754162656067102</v>
+        <v>-5.222689346006099</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-6.093554170720935</v>
+        <v>-6.081482821025432</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.295680428524236</v>
+        <v>-5.668896584586264</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.161535609537204</v>
+        <v>-6.874634960564769</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.645362133998667</v>
+        <v>-4.622117050851045</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.264822748402594</v>
+        <v>-4.104504921034511</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.202441841280326</v>
+        <v>-4.861406137914472</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.33363863653242</v>
+        <v>-0.5152783755233088</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.1107</t>
+          <t>X ≈ -0.1105</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.048246938891602</v>
+        <v>-5.638828992767408</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.913563791536227</v>
+        <v>-1.598122588320109</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.315986155278388</v>
+        <v>-4.249980082586774</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.279572493302261</v>
+        <v>-1.29650909024074</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.300475256018601</v>
+        <v>3.602448032788551</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.211058189384332</v>
+        <v>-1.773258427264118</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.463605259658728</v>
+        <v>-2.965083554567258</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.205785243863247</v>
+        <v>-3.99941148021373</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.527512892930545</v>
+        <v>-4.601509032669711</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.479789080602892</v>
+        <v>-4.865268003082051</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.520758955879572</v>
+        <v>-6.199505145349761</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.067776152361191</v>
+        <v>-6.705544199864242</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-6.069322354512074</v>
+        <v>-7.668737715971929</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.587772750797178</v>
+        <v>-8.795356174911895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.08669</t>
+          <t>X ≈ -0.08654</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>198</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.0443364947179461</v>
+        <v>-0.2502044240693024</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.576950608446666</v>
+        <v>-2.346826574909187</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>0.7942104250330004</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3162443243608166</v>
+        <v>-0.8217893217893248</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.8545338774563973</v>
+        <v>-1.311038462741244</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9819490762798182</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>0.4162424820037387</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.62409036602584</v>
+        <v>-3.079893308682635</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-1.096663897617411</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.029940813827977</v>
+        <v>-3.435643993583902</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-1.114531915867474</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.200263819732847</v>
+        <v>-3.5816177037551</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.620414673046255</v>
+        <v>-3.976775630319054</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.394679022819602</v>
+        <v>-3.727730768303559</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.0627</t>
+          <t>X ≈ -0.06256</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7434642930825319</v>
+        <v>-1.003203819524465</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.057353088849148</v>
+        <v>-5.446390155886725</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-7.382626404106112</v>
+        <v>-7.158782623548383</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.074795082911571</v>
+        <v>-0.9220283533259774</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.226984249906884</v>
+        <v>-1.029598104965011</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.315710606372178</v>
+        <v>-1.520171364772118</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.944822510039899</v>
+        <v>-3.107545011249314</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3230880650235477</v>
+        <v>-0.5199426571289365</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.160331322855221</v>
+        <v>0.9698022909861805</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6965129126257494</v>
+        <v>0.145973710171198</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.808414070967878</v>
+        <v>2.231909598512971</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.298390678921649</v>
+        <v>0.7633587786259568</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8782398256082402</v>
+        <v>0.7498802413751875</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.262276634135851</v>
+        <v>1.762283882016334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03871</t>
+          <t>X ≈ -0.03858</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.641409857694846</v>
+        <v>-4.062906855942956</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.783460148289535</v>
+        <v>-3.161611891409223</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.326379681192726</v>
+        <v>-2.002554848668026</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.825784167233991</v>
+        <v>-6.53105590062119</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.820863843786476</v>
+        <v>-5.467510010517145</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.225484124034914</v>
+        <v>-5.876498593346035</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.223416965352442</v>
+        <v>-3.85785930403987</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.444892949035719</v>
+        <v>-6.068744956654996</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.751601868822362</v>
+        <v>-5.029219500202963</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.647661051773916</v>
+        <v>-4.922800941527882</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.761431047566745</v>
+        <v>-3.001280166895903</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.712446098411014</v>
+        <v>-1.222525049981471</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.881772176579545</v>
+        <v>-4.079070250077834</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01472</t>
+          <t>X ≈ -0.0146</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.57672441376782</v>
+        <v>-4.762364077139232</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.690904518807763</v>
+        <v>-4.844039660793655</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-10.47489746044903</v>
+        <v>-10.94348335481407</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-10.04527111925588</v>
+        <v>-10.51329901329902</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-9.984758277141992</v>
+        <v>-10.40194755365034</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-9.986785445111693</v>
+        <v>-10.12916203483141</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-11.86790299000661</v>
+        <v>-11.99161992585867</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-9.340959657745437</v>
+        <v>-9.454449683239076</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-9.701343011873007</v>
+        <v>-9.791722592676109</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-9.353657017783704</v>
+        <v>-9.41434997228982</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-10.15716057125347</v>
+        <v>-10.21909102042651</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-9.224578826083786</v>
+        <v>-9.260023382160718</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-10.84233446981635</v>
+        <v>-10.85638250992567</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-10.01779642438024</v>
+        <v>-10.00673704730985</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.009272</t>
+          <t>X ≈ 0.00938</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>324</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.098199981151708</v>
+        <v>-2.81875380019563</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.07975644458583986</v>
+        <v>-0.08094323103049561</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1658858540322328</v>
+        <v>-0.1660392440365541</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.581623240173414</v>
+        <v>0.581128747795411</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3519756623863586</v>
+        <v>0.4005215821521304</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.819786110447751</v>
+        <v>-1.795828701498138</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.9785705437878605</v>
+        <v>-0.9305588647976037</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.136997212266031</v>
+        <v>-1.087749649872315</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.197979368788729</v>
+        <v>-1.124722259009111</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.356540140427299</v>
+        <v>-2.257192815132726</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.561241298687492</v>
+        <v>-2.461333262668894</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.600937220406252</v>
+        <v>-1.477240599378071</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.71244609841095</v>
+        <v>-1.563756550633251</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.05649942835871968</v>
+        <v>0.5371401632341062</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.03327</t>
+          <t>X ≈ 0.03336</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.458585748825087</v>
+        <v>4.38034753907062</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.779783997398255</v>
+        <v>2.4438135634554</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.808500157127213</v>
+        <v>3.463503136978147</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.582853414594581</v>
+        <v>3.240030287733461</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.514154999711167</v>
+        <v>-1.136144648271454</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.8609090839549225</v>
+        <v>-0.1566453485337291</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.189611873504731</v>
+        <v>1.549483014537479</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.480303745370904</v>
+        <v>-2.096561759980062</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.541285901893758</v>
+        <v>-1.780177478657571</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.679460925981545</v>
+        <v>-2.604006059472553</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.240033970362738</v>
+        <v>-3.161503397467769</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.273271476370397</v>
+        <v>-4.163407331480975</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.337550443562812</v>
+        <v>-4.205208367585513</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.179430451699268</v>
+        <v>-5.369591067407761</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.05726</t>
+          <t>X ≈ 0.05734</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.599126893154128</v>
+        <v>-3.792163106938268</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.01542480730425</v>
+        <v>-2.811237627991559</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4652031689630789</v>
+        <v>0.3206654093347296</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.557926320036422</v>
+        <v>-3.716117216117226</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.498771783675181</v>
+        <v>-2.282289433992212</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3545127890908333</v>
+        <v>0.2340858284164185</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.547757701390154</v>
+        <v>1.775993841755174</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.039155511277535</v>
+        <v>2.271699542910213</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.339195718972015</v>
+        <v>1.273188472235034</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.128254558424899</v>
+        <v>1.731411173471329</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2845757643819624</v>
+        <v>0.8862450849094117</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3189539167372857</v>
+        <v>0.9444118222743469</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.176758334989337</v>
+        <v>1.831305177761799</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.721982803107309</v>
+        <v>2.400862860290061</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.08125</t>
+          <t>X ≈ 0.08132</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.454706287062173</v>
+        <v>2.662301968216461</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0148489047140572</v>
+        <v>0.648090400301939</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4096202894690961</v>
+        <v>-0.6077165535299045</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7085796952369634</v>
+        <v>-0.908866995073943</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.246869248332658</v>
+        <v>-1.39811613602582</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5203106693413986</v>
+        <v>-0.6942961344482157</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2533480701049342</v>
+        <v>0.1071167418435124</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.072089672394249</v>
+        <v>-1.220784984057062</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.84981002634192</v>
+        <v>-2.981895524228349</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.69972882267178</v>
+        <v>-3.805724105043332</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.046060882219471</v>
+        <v>-3.147795587062184</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.157605476645365</v>
+        <v>-5.244801263490395</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.294494527383669</v>
+        <v>-7.364097121088705</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.497943426513359</v>
+        <v>-7.546086741832006</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.1052</t>
+          <t>X ≈ 0.1053</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>205</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.616644945075407</v>
+        <v>3.587449150722776</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.981068608109133</v>
+        <v>2.979881821664584</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6350777111589778</v>
+        <v>0.6349243211546565</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.228717488893672</v>
+        <v>1.740418118466899</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.178232813846762</v>
+        <v>1.738973855563749</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.03658245323801168</v>
+        <v>0.06053986218756791</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.878701362264458</v>
+        <v>2.438908163206001</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.411632718477662</v>
+        <v>1.973075402822708</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.765284708296356</v>
+        <v>5.350736940027325</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>7.842195180259239</v>
+        <v>7.453737627504971</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.686274509803866</v>
+        <v>5.786182545822655</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.232847784110518</v>
+        <v>5.356544405138706</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.837087174699434</v>
+        <v>3.985776722477318</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.747016706443965</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.1292</t>
+          <t>X ≈ 0.1293</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>156</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.288314738696386</v>
+        <v>3.25911894434379</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.95917992768387</v>
+        <v>2.957993141239143</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.923382901903189</v>
+        <v>1.923229511898867</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.151520159636576</v>
+        <v>-0.5109890109890145</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.079421056498425</v>
+        <v>4.768992617289832</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>7.581923291261717</v>
+        <v>7.60588070021133</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9.420289855072468</v>
+        <v>10.10932717508835</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.030144288208874</v>
+        <v>7.720417491628098</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>8.892239054763024</v>
+        <v>9.606521805568356</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>7.401294617407451</v>
+        <v>8.141667583727667</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>7.837619100172901</v>
+        <v>7.937527136191648</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>7.230971611502582</v>
+        <v>7.354668232530756</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9.374923322291821</v>
+        <v>9.523612870069563</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>8.959633331492633</v>
+        <v>9.131632091059366</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.1532</t>
+          <t>X ≈ 0.1533</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.040823099900429</v>
+        <v>3.694267737156764</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.33006875419074</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.107329390197542</v>
+        <v>6.826841714781182</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7.962192214945212</v>
+        <v>7.686652763295172</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.974627299530788</v>
+        <v>5.737549607744675</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>5.547363648006467</v>
+        <v>5.28040811926433</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.462653288740299</v>
+        <v>5.219752030038961</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>8.618773050750605</v>
+        <v>8.40355430615184</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>6.38387785074957</v>
+        <v>6.17680067511715</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>9.157147460216819</v>
+        <v>9.002607130798694</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.503170939637776</v>
+        <v>7.338612668663892</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.088273729674263</v>
+        <v>5.9369253914304</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.117398238679691</v>
+        <v>7.001621479465037</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.893858526587387</v>
+        <v>5.790812326881777</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.1772</t>
+          <t>X ≈ 0.1773</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>141</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>6.38433219641604</v>
+        <v>6.355136402063408</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>10.44690496860041</v>
+        <v>10.44571818215575</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.05213358384533</v>
+        <v>10.051980193841</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.345479294809607</v>
+        <v>7.344984802431604</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.80718974171387</v>
+        <v>6.855735661479642</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7.104563771348957</v>
+        <v>7.12852118029857</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.89219383761467</v>
+        <v>4.940205516604991</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.134345051984035</v>
+        <v>5.183592614377751</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.782582753617291</v>
+        <v>5.855839863396987</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.769543389911547</v>
+        <v>7.86889071520612</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.855622373495329</v>
+        <v>6.955530409514004</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>9.017660100318743</v>
+        <v>9.141356721346988</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.888289388849302</v>
+        <v>8.036978936627129</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>8.114025039075834</v>
+        <v>8.286023798642496</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5493869997687213</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.553327631310545</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.214146235625904</v>
+        <v>-1.855447950989124</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1888061806897312</v>
+        <v>0.5300751879699206</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.165668142745545</v>
+        <v>1.544585445514286</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.46304217238059</v>
+        <v>1.817370964333215</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.651059085841744</v>
+        <v>4.012353972852154</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.456717714782194</v>
+        <v>5.802160310213132</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.153311315835218</v>
+        <v>6.51706740032445</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.303392519505358</v>
+        <v>5.693238819509425</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.613842876396632</v>
+        <v>6.992857770469577</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.648221028751998</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.743221690590104</v>
+        <v>8.159625979766879</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>7.656791142534139</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.083325669088637</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.080053930827091</v>
+        <v>-1.654264519798936</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.754090347068363</v>
+        <v>5.269070662618034</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.089134767765195</v>
+        <v>6.618466898954701</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10.16530304599477</v>
+        <v>9.787754343368526</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.053038521413058</v>
+        <v>7.62151547194356</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.173147439255317</v>
+        <v>8.78037157784005</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.706078795468684</v>
+        <v>8.314538817456743</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>11.05473519316271</v>
+        <v>10.71659059856383</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>11.40963567394128</v>
+        <v>11.11227421287089</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>12.40975379278959</v>
+        <v>12.12764596045675</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>12.44413194514484</v>
+        <v>12.18581269782164</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>16.84325820026517</v>
+        <v>16.66870355174562</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>13.4545360191664</v>
+        <v>13.25921182839512</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>11.67002736569206</v>
+        <v>12.8745035597284</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>10.05884127262823</v>
+        <v>9.368249551495623</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.55086234070344</v>
+        <v>10.8975884862579</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>17.34146484278231</v>
+        <v>16.7967032967033</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>9.256005478365914</v>
+        <v>8.615146463443786</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.666587055170815</v>
+        <v>6.964855059185801</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11.35546160156503</v>
+        <v>10.75035281611413</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10.88839295777823</v>
+        <v>10.28452005573073</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.16703344276489</v>
+        <v>4.478316677363161</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5435297407746518</v>
+        <v>-0.1916657496056615</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3388285825144024</v>
+        <v>-0.3958061971417521</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.033584093360346</v>
+        <v>5.431591309453907</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.500225692877123</v>
+        <v>6.959510305967001</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.725961343103656</v>
+        <v>7.208555167982368</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.460507867269044</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.132387672320185</v>
+        <v>7.906711089957163</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.737616287565146</v>
+        <v>7.512973101642459</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.908657757684125</v>
+        <v>9.642857142857139</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.288735551527203</v>
+        <v>5.153608001905162</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.667742234223518</v>
+        <v>9.426393520724091</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.621049757695715</v>
+        <v>-0.6342625685013132</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.075146904639993</v>
+        <v>6.899904671115344</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>12.13661372770905</v>
+        <v>12.86293206197855</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>17.40914391097104</v>
+        <v>18.03910348116356</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>15.16362642618029</v>
+        <v>15.83496303362747</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>17.23882090506617</v>
+        <v>17.89312977099237</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>20.90030270481398</v>
+        <v>21.49797184442854</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>17.04440570197929</v>
+        <v>17.74701670644391</v>
       </c>
     </row>
     <row r="29">
@@ -1771,98 +1771,98 @@
         <v>49</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.661941112322857</v>
+        <v>4.632745317970226</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-9.19414293992471</v>
+        <v>-9.195329726369366</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.778432614095763</v>
+        <v>8.778279224091442</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.908657757684061</v>
+        <v>8.908163265306058</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.288735551527147</v>
+        <v>4.337281471292918</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>10.70855856075407</v>
+        <v>10.73251596970368</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.66466452801856</v>
+        <v>12.71267620700888</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>14.23841221076244</v>
+        <v>14.28765977315616</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>12.13661372770899</v>
+        <v>12.20987083748869</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.36832758444042</v>
+        <v>15.467674909735</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.000361120057718</v>
+        <v>7.100269156076394</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.15718825200488</v>
+        <v>13.28088487303312</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.81867005175276</v>
+        <v>16.96735959953059</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>23.16685468157117</v>
+        <v>23.33885344113784</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.3212</t>
+          <t>X ≈ 0.3211</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>46</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3070029870561513</v>
+        <v>-0.3361987814087826</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.951376137271389</v>
+        <v>8.950189350826733</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>-0.1392008114010252</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.512916852626475</v>
+        <v>6.512422360248472</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>12.4963664299656</v>
+        <v>12.54491234973137</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.31547959003547</v>
+        <v>19.33943699898508</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.23076923076923</v>
+        <v>19.27878090975955</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>18.76370058698249</v>
+        <v>18.8129481493762</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>16.52880538698152</v>
+        <v>16.60206249676121</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>15.67888659065163</v>
+        <v>15.7782339159462</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.30027238891321</v>
+        <v>13.40018042493189</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.638998367355484</v>
+        <v>4.762694988383728</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.566673600998541</v>
+        <v>8.715363148776369</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.96632229470327</v>
+        <v>11.13832105426993</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>41</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.055669335319301</v>
+        <v>6.02647354096667</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.005458852011536</v>
+        <v>2.00427206556688</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.610687467256497</v>
+        <v>1.610534077252176</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.618961391332732</v>
+        <v>6.618466898954729</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.641647447993073</v>
+        <v>3.690193367758845</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.378045867872125</v>
+        <v>6.402003276821738</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.023737662125775</v>
+        <v>-0.9757259831354546</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.948218084331387</v>
+        <v>0.9974656467251037</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.326260318052505</v>
+        <v>3.399517427832201</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.79341469245432</v>
+        <v>9.892762017748893</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.149689143950262</v>
+        <v>7.249597179968937</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.623091686549493</v>
+        <v>9.746788307577738</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.763916442992176</v>
+        <v>6.912605990770004</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.111603312730935</v>
+        <v>2.283602072297597</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>32</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6440839694656475</v>
+        <v>0.6148881751130162</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.28289787640184</v>
+        <v>5.281711089957184</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.013126491646823</v>
+        <v>8.012973101642501</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>17.51835163523514</v>
+        <v>17.51785714285714</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.605062082139511</v>
+        <v>7.653608001905283</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.472563888225487</v>
+        <v>-1.448606479275874</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.557274247491634</v>
+        <v>-1.509262568501313</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.274342891278351</v>
+        <v>-8.225095328884635</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11.46032504780115</v>
+        <v>-11.38706793802145</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.264945002391222</v>
+        <v>-6.165036966372547</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-12.4805668500359</v>
+        <v>-12.35687022900765</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-16.02571770334929</v>
+        <v>-15.87702815557146</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-18.9249820531228</v>
+        <v>-18.75298329355613</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>18</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.019008987512969</v>
+        <v>7.017822201068313</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.754462746346256</v>
+        <v>6.753968253968253</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.77172874880608</v>
+        <v>11.82027466857185</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.9579916673300488</v>
+        <v>0.9819490762796619</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.42883686361948</v>
+        <v>6.476848542609801</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.51732377538826</v>
+        <v>11.56657133778197</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.900786063309965</v>
+        <v>5.974043173089662</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6750112944802851</v>
+        <v>-0.5513146734520404</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.095162147793772</v>
+        <v>-0.9464726000159445</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.8694264975672397</v>
+        <v>-0.6974277380005773</v>
       </c>
     </row>
     <row r="34">
@@ -2028,49 +2028,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.112494977902813</v>
+        <v>-8.065667380442541</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.723681070966606</v>
+        <v>-9.648844465598394</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.671021228488883</v>
+        <v>6.624084212753573</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.801246372077244</v>
+        <v>6.753968253968253</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>18.7892726084552</v>
+        <v>17.37583022412749</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>0.9819490762796619</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.212462594613633</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.00855184556373</v>
+        <v>6.011015782226458</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.684411794304118</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.834492997974259</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.892949734450944</v>
+        <v>4.946074144738624</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.59898790266746</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.507177033492859</v>
+        <v>4.609082955539691</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.469754788982542</v>
+        <v>-0.6974277380004992</v>
       </c>
     </row>
   </sheetData>
@@ -2210,989 +2210,989 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.2666</t>
+          <t>X &gt; -0.2664</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4047</v>
+        <v>4057</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.04249238521415322</v>
+        <v>-0.02853934331450603</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.009893441812018011</v>
+        <v>-0.001374434741777009</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.07583358720980016</v>
+        <v>-0.08683024152372099</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1540355967096474</v>
+        <v>-0.1648635357757655</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1119004425153847</v>
+        <v>-0.1243064102934994</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.09694736541412396</v>
+        <v>-0.1086618298293658</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02021208666283059</v>
+        <v>-0.03288461574540946</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.09368696315043934</v>
+        <v>0.08080548332307558</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1450550114288589</v>
+        <v>0.1312727808362482</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.04935872313632927</v>
+        <v>0.03516356488678696</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.006659935880399814</v>
+        <v>-0.007401498392233918</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1426439060991029</v>
+        <v>-0.157128913412663</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.005460786353239655</v>
+        <v>-0.02100302003671572</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.03753456115340015</v>
+        <v>-0.05382135123417697</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.2426</t>
+          <t>X &gt; -0.2424</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4020</v>
+        <v>4031</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01376998540665397</v>
+        <v>-0.0125846240956875</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.04976295576690148</v>
+        <v>0.0496742361357434</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05869191569630772</v>
+        <v>-0.05852615615071244</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.0390304987598924</v>
+        <v>-0.03890479725669138</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09225735196331186</v>
+        <v>-0.09391675057002402</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.02954005505764457</v>
+        <v>-0.0304027159681084</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.00137034880774678</v>
+        <v>-0.003257120259611668</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.01707538989401058</v>
+        <v>0.01508921409280362</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1685569397764937</v>
+        <v>0.1652115466167956</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.003374446127445196</v>
+        <v>-0.0005495547720002492</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01339143540138821</v>
+        <v>-0.01729279185591537</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1390700822586481</v>
+        <v>-0.1435674767140611</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.02301315224259071</v>
+        <v>-0.02881386985716716</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1065740929237506</v>
+        <v>-0.113067639872142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.2186</t>
+          <t>X &gt; -0.2184</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3986</v>
+        <v>3997</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.007205999973272981</v>
+        <v>0.008591417008275926</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1350114331802104</v>
+        <v>0.1346981191414969</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.04604288538599377</v>
+        <v>-0.04590913388648232</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.02731903543552505</v>
+        <v>-0.02722022175478855</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02635218569534459</v>
+        <v>-0.02861865810476161</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1094967026608629</v>
+        <v>0.1080414607990576</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.08857473823338324</v>
+        <v>0.08601715177840674</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1612783512065974</v>
+        <v>0.158460754053138</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2644932934666997</v>
+        <v>0.2602334113038793</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.05504437642036208</v>
+        <v>0.05010073185089681</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.03989330294848514</v>
+        <v>0.0349630336274771</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.08713655916325536</v>
+        <v>-0.09286672813241381</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.01665700608316456</v>
+        <v>-0.02378903601167792</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.07776679973590461</v>
+        <v>-0.08585794954808534</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1947</t>
+          <t>X &gt; -0.1945</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3942</v>
+        <v>3953</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.09153549956090501</v>
+        <v>-0.08953693835142928</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.02027612460981487</v>
+        <v>-0.02014893526352068</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1989908875588853</v>
+        <v>-0.1984295219700627</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1309398627405614</v>
+        <v>-0.1305468440214881</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1493039011559176</v>
+        <v>-0.1517933105632352</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.04060186290900702</v>
+        <v>-0.04192256107337755</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.0608511023916094</v>
+        <v>-0.06355549779424052</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01783036100125912</v>
+        <v>0.01483268323961795</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.09750368288037947</v>
+        <v>0.09284616000785917</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.07950385426786255</v>
+        <v>-0.08523313748693084</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1686205410477299</v>
+        <v>-0.1741370674847573</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3228589392853749</v>
+        <v>-0.3293733895638908</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2216028162075148</v>
+        <v>-0.2298986664465232</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3113341586529472</v>
+        <v>-0.3207799037255867</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.1707</t>
+          <t>X &gt; -0.1705</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3875</v>
+        <v>3886</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.06322055728332998</v>
+        <v>-0.0607658387366854</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01440724322771558</v>
+        <v>-0.01427403061749288</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2665955876120947</v>
+        <v>-0.2658311067229491</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2253742334907258</v>
+        <v>-0.2246993253153491</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2090470836689988</v>
+        <v>-0.2122456566313602</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1036159098582274</v>
+        <v>-0.1051935362866345</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.09700892034067721</v>
+        <v>-0.1004839915683533</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.04261794355801385</v>
+        <v>0.03865081705573203</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.07318010683803067</v>
+        <v>0.06724971810808</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.0148713254406232</v>
+        <v>-0.02259317693411589</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2309068383891386</v>
+        <v>-0.2380634513301061</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3110414437939326</v>
+        <v>-0.319833191970595</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2523688901397918</v>
+        <v>-0.2632836225125459</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3733691498969449</v>
+        <v>-0.3600342456919634</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.1467</t>
+          <t>X &gt; -0.1465</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3799</v>
+        <v>3809</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.05373156451493344</v>
+        <v>-0.06310842263626171</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.0811262228585079</v>
+        <v>0.06901475487862285</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2206619042576605</v>
+        <v>-0.2058014466686231</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2074887008993187</v>
+        <v>-0.2188505575095405</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2850088398463697</v>
+        <v>-0.2747388673638369</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2623037726185373</v>
+        <v>-0.2759125589404192</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2276093329055655</v>
+        <v>-0.2436990036258209</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1020242792909869</v>
+        <v>-0.1184487635988631</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.09594166626025924</v>
+        <v>-0.1147757796160036</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.08970202403632044</v>
+        <v>-0.1109489847336036</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.200751369136789</v>
+        <v>-0.2101576379360139</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2568826395095556</v>
+        <v>-0.2685075945284865</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1358453685243362</v>
+        <v>-0.150322118826054</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1996595998455746</v>
+        <v>-0.1752726083368756</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.1227</t>
+          <t>X &gt; -0.1225</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3683</v>
+        <v>3687</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2174299909572284</v>
+        <v>-0.2078366352878476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1231323572909488</v>
+        <v>0.1738473673887597</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3653984541232802</v>
+        <v>-0.3677857059456144</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.208058343072878</v>
+        <v>-0.223231227975063</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2977043946709728</v>
+        <v>-0.2910774644722238</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2173089384017644</v>
+        <v>-0.2352116853496042</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.08504072430205412</v>
+        <v>-0.07894803487875635</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.0866853235886893</v>
+        <v>0.0788634563648003</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.06782963333861147</v>
+        <v>0.06900581469003697</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1015368290503176</v>
+        <v>0.1128561926603169</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.06076362851121075</v>
+        <v>-0.06416928741374051</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1621443683633217</v>
+        <v>-0.1415773873590354</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.03925965284697952</v>
+        <v>0.005564035317910054</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2479524576842564</v>
+        <v>-0.16402207847608</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.09869</t>
+          <t>X &gt; -0.09853</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.06821527108910885</v>
+        <v>0.06603391949104065</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2229078450717097</v>
+        <v>0.2632031172920222</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1718635396833292</v>
+        <v>-0.1720169296876506</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1555660520334428</v>
+        <v>-0.1691086691086738</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5229641212214133</v>
+        <v>-0.487417639120423</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1686262636170923</v>
+        <v>-0.1576520633214358</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.03148251696293158</v>
+        <v>0.06659213235339223</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2479798088070737</v>
+        <v>0.2845200557307308</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2439614802535388</v>
+        <v>0.3045275035739863</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2769820174468904</v>
+        <v>0.3638898059498885</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1577266011405598</v>
+        <v>0.2452194438838831</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.07817709755740054</v>
+        <v>0.1894260672886645</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.2561464379210108</v>
+        <v>0.3925587390154348</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1116172063474821</v>
+        <v>0.2712332306604281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.0747</t>
+          <t>X &gt; -0.07455</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.06964237574395327</v>
+        <v>0.0849394726386663</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3902401643583531</v>
+        <v>0.4192375010649201</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.246004205606468</v>
+        <v>-0.2297805215459476</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1459631851693288</v>
+        <v>-0.1300897170462463</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5031479993576866</v>
+        <v>-0.4381794377083068</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2359580928738225</v>
+        <v>-0.2257803923193364</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.0188272206277702</v>
+        <v>0.04568912231994915</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4196278301221739</v>
+        <v>0.4856534633858729</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2982774272969522</v>
+        <v>0.3882943808191257</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4746188181086524</v>
+        <v>0.5910358483133251</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2095494135460143</v>
+        <v>0.3265089273472839</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2741116890525603</v>
+        <v>0.4148689014271483</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4878274219148224</v>
+        <v>0.6537689458778217</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3211694711754589</v>
+        <v>0.510301730598492</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.05071</t>
+          <t>X &gt; -0.05057</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3054</v>
+        <v>3050</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1385993591185652</v>
+        <v>0.1784127652769456</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8522331743716904</v>
+        <v>0.9231045325801119</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3592299625046707</v>
+        <v>0.3654321180358977</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.06719191420820891</v>
+        <v>-0.06206088992975367</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4417617554505995</v>
+        <v>-0.3873756046521564</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1443877258155126</v>
+        <v>-0.1145900858332283</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2293171081075727</v>
+        <v>0.3165571036298331</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4826151964753933</v>
+        <v>0.5720358186563246</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2251693857286483</v>
+        <v>0.3383418980441206</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4558006876306138</v>
+        <v>0.6292674155897942</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.01085200959487054</v>
+        <v>0.1628318860864937</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1872458546137636</v>
+        <v>0.3849330496808889</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4547177910842422</v>
+        <v>0.6455128280351019</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.156550363380191</v>
+        <v>0.4027544113619399</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02672</t>
+          <t>X &gt; -0.02659</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7058971562788372</v>
+        <v>0.6790377352303167</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.402403370907315</v>
+        <v>1.405244814297333</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6779616564819477</v>
+        <v>0.6449379110266165</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7349267268102366</v>
+        <v>0.7015081692500971</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1966371737145423</v>
+        <v>0.2122590282981776</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3841210934595196</v>
+        <v>0.411730764125906</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9953814301640449</v>
+        <v>1.047555613316867</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.041133299197817</v>
+        <v>1.094919333871935</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.016781179305077</v>
+        <v>1.094603616230742</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.19250340861624</v>
+        <v>1.297167997292604</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6581319206857188</v>
+        <v>0.7631155262961045</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6558800364110056</v>
+        <v>0.7846253721653937</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7119196592880712</v>
+        <v>0.8660070350443831</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7545051263644211</v>
+        <v>0.9317674395817406</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.002725</t>
+          <t>X &gt; -0.002611</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.442289311702702</v>
+        <v>1.435608425634939</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.251804387253237</v>
+        <v>2.27414324027032</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.232659045903873</v>
+        <v>2.256188132957703</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.237675508357007</v>
+        <v>2.260811213838352</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.615913501171164</v>
+        <v>1.68805476599708</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.829815076716102</v>
+        <v>1.877332977926656</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.788510393576814</v>
+        <v>2.860518224818101</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.488386657970381</v>
+        <v>2.56170007821347</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.510876955537753</v>
+        <v>2.608234775966025</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.662627608289689</v>
+        <v>2.786493877823268</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.165772860713972</v>
+        <v>2.290077856174449</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.033206104888997</v>
+        <v>2.181229979760637</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.322571111341865</v>
+        <v>2.495884161756301</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.256153172252873</v>
+        <v>2.452653449658939</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.02127</t>
+          <t>X &gt; 0.02137</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.152288602670282</v>
+        <v>2.101187064538415</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.616392084896027</v>
+        <v>2.642587478175415</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.607721086241376</v>
+        <v>2.635136307823046</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.496633488516999</v>
+        <v>2.523591087811269</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.813556290633656</v>
+        <v>1.889484390123471</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.400505609844039</v>
+        <v>2.451985022414156</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.377571312353922</v>
+        <v>3.453617682585119</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.055290313354831</v>
+        <v>3.132642478937655</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.090833253357147</v>
+        <v>3.192241574291437</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.447478163591001</v>
+        <v>3.575559299608763</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.904939167492969</v>
+        <v>3.033417886355629</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.601479482010454</v>
+        <v>2.753583658003478</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.953529400897814</v>
+        <v>3.130999367364318</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.600114471973768</v>
+        <v>2.752328150190884</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.04526</t>
+          <t>X &gt; 0.04535</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.790440753385248</v>
+        <v>1.740447459229344</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.747652203593333</v>
+        <v>2.674048897563431</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.576219735644543</v>
+        <v>2.504024555781157</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.483105962426656</v>
+        <v>2.410194950463406</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.335659513741909</v>
+        <v>2.368373102576356</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.912207189384809</v>
+        <v>2.86487226792773</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.720852497343657</v>
+        <v>3.754999176465134</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.923800603975671</v>
+        <v>3.960307355679106</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.974487905856023</v>
+        <v>3.979263158175421</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.40876788116212</v>
+        <v>4.553644868188179</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.869058347692551</v>
+        <v>4.013933950853421</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.680097583241619</v>
+        <v>3.848387041685875</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.097467667951655</v>
+        <v>4.292155289618691</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.820690755364126</v>
+        <v>4.037844446936077</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.06925</t>
+          <t>X &gt; 0.06933</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.931803861211243</v>
+        <v>2.909942375655021</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.756341719432946</v>
+        <v>3.833540358249842</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.023275341443806</v>
+        <v>2.965547627387721</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.762431472853542</v>
+        <v>3.705187766163377</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.359459917051488</v>
+        <v>3.351439980225003</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.453856950746115</v>
+        <v>3.420973466523613</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.181054575241788</v>
+        <v>4.173325507379445</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.32291691927643</v>
+        <v>4.317248844557078</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4.532570757340935</v>
+        <v>4.551278945447379</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.103490932594298</v>
+        <v>5.150214592274679</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.628153779746825</v>
+        <v>4.675071434711491</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.391895937514867</v>
+        <v>4.462235462049279</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.715994069316473</v>
+        <v>4.812334988059973</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.265139733074804</v>
+        <v>4.383873075007592</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.09324</t>
+          <t>X &gt; 0.09331</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.021092001594162</v>
+        <v>2.9561261172352</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.462114743871695</v>
+        <v>4.427611411500578</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.665736933413854</v>
+        <v>3.631944162735707</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.599174928407834</v>
+        <v>4.565686724850714</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.221527945593266</v>
+        <v>4.237209288078859</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4.197616834666107</v>
+        <v>4.188451398537651</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.916119326805557</v>
+        <v>4.931653830212511</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.332584819565</v>
+        <v>5.35006544281952</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.914172944166722</v>
+        <v>5.956179650402987</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.75100113578867</v>
+        <v>6.820453963478677</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>6.064372266685098</v>
+        <v>6.133998403402401</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.179071704180998</v>
+        <v>6.272550992857319</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.96374012797601</v>
+        <v>7.08318084764398</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.466584211937487</v>
+        <v>6.608753040849059</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.1172</t>
+          <t>X &gt; 0.1173</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.903699354081034</v>
+        <v>2.831562862312246</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.754051722555666</v>
+        <v>4.713255844528859</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.26312649164678</v>
+        <v>4.223271465453813</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.066428558312062</v>
+        <v>5.123126632751273</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.624292851370214</v>
+        <v>4.730123882559695</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5.017820727159148</v>
+        <v>5.002909401378623</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.423485265954895</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.908349416413941</v>
+        <v>6.016362803935358</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.943521106045011</v>
+        <v>6.075636585558911</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.535910002022838</v>
+        <v>6.695503866149132</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.138901151454952</v>
+        <v>6.202624246332</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>6.365586996117969</v>
+        <v>6.453283765217584</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7.580051527419954</v>
+        <v>7.694314481579646</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>7.036556408415706</v>
+        <v>7.173388217512247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.1412</t>
+          <t>X &gt; 0.1413</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.835826050913617</v>
+        <v>2.756026340458426</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.070793804003628</v>
+        <v>5.023358881576641</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.676022419248589</v>
+        <v>4.629620893261936</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.163713626185363</v>
+        <v>6.118508331985119</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.720446697524061</v>
+        <v>4.723256926027531</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.565332039376344</v>
+        <v>4.543041312343625</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.59374385205588</v>
+        <v>4.59563550624388</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.710385615508955</v>
+        <v>5.715306709620442</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.423159115094776</v>
+        <v>5.451833534232222</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.383195069896139</v>
+        <v>6.440009483428575</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.839127395798847</v>
+        <v>5.896118186515352</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.21287206399127</v>
+        <v>6.294035773257377</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.263309445971977</v>
+        <v>7.371131527327748</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.697189892578599</v>
+        <v>6.827424407463155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.1652</t>
+          <t>X &gt; 0.1653</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>746</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.612917749626511</v>
+        <v>2.58372195527388</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.682696804015762</v>
+        <v>3.681510017571107</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.226263220869292</v>
+        <v>4.226109830864971</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.831019195556856</v>
+        <v>5.830524703178853</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.488440098225233</v>
+        <v>4.536986017991005</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.383669355742356</v>
+        <v>4.407626764691969</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.433007253848842</v>
+        <v>4.481018932839163</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.172372926415996</v>
+        <v>5.221620488809712</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.245439027265874</v>
+        <v>5.318696137045571</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.870051062035209</v>
+        <v>5.969398387329782</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.531301646402362</v>
+        <v>5.631209682421037</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.235921085620959</v>
+        <v>6.359617706649203</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.290301063406744</v>
+        <v>7.438990611184572</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.845795426770003</v>
+        <v>7.017794186336666</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>605</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.733960002523496</v>
+        <v>1.704764208170864</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.106244983839836</v>
+        <v>2.105058197395181</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.868498392473228</v>
+        <v>2.868345002468907</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.4780623790368</v>
+        <v>5.477567886658797</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.948037288751017</v>
+        <v>3.996583208516789</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.749543549791063</v>
+        <v>3.773500958740676</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.325990215318292</v>
+        <v>4.374001894308613</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.181235621118319</v>
+        <v>5.230483183512035</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.120253464595542</v>
+        <v>5.193510574375239</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.427359461654113</v>
+        <v>5.526706786948687</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.222658303393921</v>
+        <v>5.322566339412596</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.587614968145935</v>
+        <v>5.71131158917418</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.150935189212703</v>
+        <v>7.29962473699053</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.550224558447489</v>
+        <v>6.722223318014152</v>
       </c>
     </row>
     <row r="26">
@@ -3254,49 +3254,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.064538514920187</v>
+        <v>2.150905124265556</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.510434874287654</v>
+        <v>1.415185666228346</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.28691084682648</v>
+        <v>4.199413779608562</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.954133876249934</v>
+        <v>6.871670702179173</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.724512399264178</v>
+        <v>4.68750630698996</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.387636957440499</v>
+        <v>4.324698605469905</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.514343088660588</v>
+        <v>4.475906923024105</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.104356897305145</v>
+        <v>5.069396196539067</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.831958250296104</v>
+        <v>4.82055918062261</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.461954887370048</v>
+        <v>5.47978144726526</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.834420748137347</v>
+        <v>4.851912186169848</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.291631881465179</v>
+        <v>5.333807737094062</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.985645933014347</v>
+        <v>7.057293878326846</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.365715621295848</v>
+        <v>6.458881113223569</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>390</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.16010961049129</v>
+        <v>3.130913816138658</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.061744030247972</v>
+        <v>2.060557243803316</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.974664953185247</v>
+        <v>3.974511563180926</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.925402917286426</v>
+        <v>6.924908424908423</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.566600543677914</v>
+        <v>3.615146463443686</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.607564316902746</v>
+        <v>3.631521725852359</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.522853957636578</v>
+        <v>3.570865636626898</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.337836595901116</v>
+        <v>4.387084158294833</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.507623670147574</v>
+        <v>3.58088077992727</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.196166412279247</v>
+        <v>4.29551373757382</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.222234484788288</v>
+        <v>3.322142520806963</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.887743835112254</v>
+        <v>5.036433382890081</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.85706922892853</v>
+        <v>5.029067988495193</v>
       </c>
     </row>
     <row r="28">
@@ -3358,49 +3358,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.82175459261105</v>
+        <v>1.631900009432542</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.8040403096362354</v>
+        <v>0.9362968887737324</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.783156165237287</v>
+        <v>2.909422805784473</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.287268549181732</v>
+        <v>5.406170752324599</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.671827660774461</v>
+        <v>2.845915694212906</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.969201690409548</v>
+        <v>3.118701213031834</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.291019521054359</v>
+        <v>2.466329147475022</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.307630402490169</v>
+        <v>3.479786327920074</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.246648245967393</v>
+        <v>3.442813718783277</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.770616689993624</v>
+        <v>4.98584904329374</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.675707816599903</v>
+        <v>3.894134631260606</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.413350063910713</v>
+        <v>3.656443380459827</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.476878735819852</v>
+        <v>4.740575394724402</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.405878481001878</v>
+        <v>4.693762268574083</v>
       </c>
     </row>
     <row r="29">
@@ -3413,150 +3413,150 @@
         <v>288</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.380195080576762</v>
+        <v>2.35099928622413</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2726576791537383</v>
+        <v>-0.273844465598394</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.110348713869001</v>
+        <v>2.11019532386468</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.67112941301292</v>
+        <v>4.670634920634917</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.396728748806112</v>
+        <v>2.445274668571884</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.999658333996756</v>
+        <v>2.023615742946369</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.956614641397252</v>
+        <v>3.004626320387572</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.836768219832742</v>
+        <v>2.886015782226458</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.734119396643294</v>
+        <v>1.80737650642299</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.620311711424549</v>
+        <v>2.719659036719122</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.721166108719913</v>
+        <v>1.821074144738589</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.061099816630787</v>
+        <v>1.184796437659031</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.255573502432803</v>
+        <v>2.427572261999465</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.3092</t>
+          <t>X &gt; 0.3091</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>239</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.912389408796187</v>
+        <v>1.883193614443556</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.556433441255372</v>
+        <v>1.555246654810716</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7432520146593333</v>
+        <v>0.743098624655012</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.802347451134729</v>
+        <v>3.801852958756726</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.008827772516021</v>
+        <v>2.057373692281793</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.214151592946088</v>
+        <v>0.2381090018957011</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.9662613173619192</v>
+        <v>1.01427299635224</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.4991926735751804</v>
+        <v>0.5484402359688971</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3986095666295952</v>
+        <v>-0.3253524568498989</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.006701762563551483</v>
+        <v>0.1060490878581248</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.6388206879853726</v>
+        <v>0.7387287240040479</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.418851368864324</v>
+        <v>-1.295154747836079</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.420592180336733</v>
+        <v>-1.271902632558906</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.031676613792214</v>
+        <v>-1.859677854225552</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.3332</t>
+          <t>X &gt; 0.3331</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>193</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.441363762211758</v>
+        <v>2.412167967859126</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.206091760903881</v>
+        <v>-0.2072785473485368</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.9535409994187987</v>
+        <v>0.9533876094144773</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.156305003110795</v>
+        <v>3.155810510732792</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4907928401403439</v>
+        <v>-0.442246920374572</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.338496530712511</v>
+        <v>-4.314539121762898</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.386937459926862</v>
+        <v>-3.338925780936542</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.854006103713601</v>
+        <v>-3.804758541319885</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.433122975262286</v>
+        <v>-4.35986586548259</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.728637626514434</v>
+        <v>-3.629290301219861</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.378934639696901</v>
+        <v>-2.279026603678226</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.862691202367486</v>
+        <v>-2.738994581339242</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.800976770706804</v>
+        <v>-3.652287222928976</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-5.129645265557983</v>
+        <v>-4.95764650599132</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>152</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.466452390518278</v>
+        <v>1.437256596165646</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.8026284393876466</v>
+        <v>-0.8038152258323024</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.7762843863836295</v>
+        <v>0.7761309963793082</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.22229900365619</v>
+        <v>2.221804511278187</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.605464233650018</v>
+        <v>-1.556918313884246</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.22914283559389</v>
+        <v>-7.205185426644277</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-4.024379510649531</v>
+        <v>-3.976367831659211</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.526114521485361</v>
+        <v>-6.452857411705665</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.376033317815221</v>
+        <v>-7.276685992520648</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-4.949155528706989</v>
+        <v>-4.849247492688313</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-7.082876789964864</v>
+        <v>-6.910878030398202</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>120</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.685750636132312</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.42543545693151</v>
+        <v>-2.426622243376165</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.153693565024206</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.856648364764858</v>
+        <v>-1.857142857142861</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.061604584527224</v>
+        <v>-4.013058664761452</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-8.764230554892137</v>
+        <v>-8.740273145942524</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.316009557945044</v>
+        <v>-4.266761995551327</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-7.726910510797673</v>
+        <v>-7.627563185503099</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.59827833572453</v>
+        <v>-4.498370299705854</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-4.563900183369206</v>
+        <v>-4.440203562340962</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.150717703349287</v>
+        <v>-4.002028155571459</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.924982053122754</v>
+        <v>-3.752983293556092</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.421044753779377</v>
+        <v>2.391848959426746</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.506481351490478</v>
+        <v>-3.5066347414948</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-3.376256207902117</v>
+        <v>-3.37675070028012</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.855722231586043</v>
+        <v>-6.807176311820271</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.47991682940194</v>
+        <v>-10.45595942045232</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.643058561217124</v>
+        <v>-6.595046882226804</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-7.110127205003863</v>
+        <v>-7.060879642610146</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7.171109361526639</v>
+        <v>-7.097852251746943</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-8.021028157856499</v>
+        <v>-7.921680832561925</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.304160688665704</v>
+        <v>-4.204252652647028</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.250174693173136</v>
+        <v>-5.126478072144891</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.689933389623789</v>
+        <v>-4.541243841845962</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-4.464197739397257</v>
+        <v>-4.292198979830594</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.4291</t>
+          <t>X &gt; 0.429</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.145589993562041</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.489692485043967</v>
+        <v>-2.902812719566647</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-6.294102424015868</v>
+        <v>-5.677503088833731</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.163877280427506</v>
+        <v>-5.547619047619051</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-12.72626321906537</v>
+        <v>-11.98924914095193</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-13.63370846653872</v>
+        <v>-12.90693981260918</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-8.899141717371151</v>
+        <v>-8.205691139929883</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-10.57102963826632</v>
+        <v>-9.862000090789415</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.427192517680666</v>
+        <v>-8.708496509450022</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-10.27711131401053</v>
+        <v>-9.532325090265005</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-6.867354640945422</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.628157211481664</v>
+        <v>-4.916394038531443</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-7.253127341903507</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-5.82257241456854</v>
+        <v>-5.062507103079902</v>
       </c>
     </row>
   </sheetData>
@@ -3904,989 +3904,989 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.2666</t>
+          <t>X &lt; -0.2664</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.350409270670461</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.534403900498212</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.344451792851594</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.293954044873701</v>
+        <v>8.738095238095234</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.755664491778006</v>
+        <v>8.248846097143314</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.848219244304651</v>
+        <v>7.331155425486052</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.558689607930056</v>
+        <v>6.080023145784395</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.9324754213988555</v>
+        <v>-0.3381905669798897</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.9934575779216317</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.5662621799653849</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.566380298813613</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.624854836711101</v>
+        <v>8.178844056706659</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.385426874963969</v>
+        <v>3.021781368238067</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.611162525190501</v>
+        <v>3.270826230253434</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.2426</t>
+          <t>X &lt; -0.2424</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.973629424011101</v>
+        <v>2.944433629658469</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.87676285528314</v>
+        <v>1.876609465278818</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.006987998871502</v>
+        <v>2.006493506493499</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.675163384501808</v>
+        <v>2.699120793451421</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.499543934326546</v>
+        <v>3.547555613316867</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.123384381448901</v>
+        <v>2.172631943842617</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.573961411437509</v>
+        <v>-1.500704301657812</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.121574337687171</v>
+        <v>2.220921662981745</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.916873179426979</v>
+        <v>2.016781215445654</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.587614968145935</v>
+        <v>5.71131158917418</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.440191387559807</v>
+        <v>2.588880935337635</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.484108855968159</v>
+        <v>4.656107615534822</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.2186</t>
+          <t>X &lt; -0.2184</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>144</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.685750636132312</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.008768790264845</v>
+        <v>-2.009955576709501</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.198907190790699</v>
+        <v>1.198412698412696</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.04950652658389</v>
+        <v>2.098052446349662</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.819786110447687</v>
+        <v>-1.795828701498074</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1788368636194804</v>
+        <v>0.226848542609801</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.371565113500594</v>
+        <v>-2.322317551106877</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.821436158912263</v>
+        <v>-3.748179049132567</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1897561558689915</v>
+        <v>0.2891034811635649</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>0.08496303362747426</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.797210927741901</v>
+        <v>2.920907548770145</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.602795724655024</v>
+        <v>2.774794484221687</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1947</t>
+          <t>X &lt; -0.1945</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>188</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.370147799252877</v>
+        <v>3.340952004900245</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.758961706189048</v>
+        <v>1.757774919744392</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.02376478951912</v>
+        <v>4.023611399514799</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.090160145873448</v>
+        <v>3.089665653495445</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.147615273628816</v>
+        <v>4.196161193394587</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.785414835178784</v>
+        <v>1.809372244128397</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.296449156763686</v>
+        <v>3.344460835754006</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.233635832125877</v>
+        <v>1.282883394519594</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.6407387819860801</v>
+        <v>0.7139958917657765</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.98230934735836</v>
+        <v>3.081656672652933</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.37335286994923</v>
+        <v>4.473260905967905</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.067305490389657</v>
+        <v>7.191002111417902</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.583324849842207</v>
+        <v>5.732014397620034</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.872890287302781</v>
+        <v>7.044889046869443</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.1707</t>
+          <t>X &lt; -0.1705</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>255</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.028887891034273</v>
+        <v>1.999692096681642</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.202015523460645</v>
+        <v>1.200828737015989</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.944499040666393</v>
+        <v>3.944345650662072</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.682567321509659</v>
+        <v>3.682072829131656</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.928591493904158</v>
+        <v>3.977137413669929</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.265181209813747</v>
+        <v>2.28913861876336</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.964784576037772</v>
+        <v>3.012796255028093</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5369316185255499</v>
+        <v>0.5861791809192667</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.8681063247478704</v>
+        <v>0.9413634345275668</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.194658116653301</v>
+        <v>1.294005441947874</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.127211860353896</v>
+        <v>4.227119896372571</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.945903738199419</v>
+        <v>5.069600359227664</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.52575288488601</v>
+        <v>4.674442432663838</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.927959123347833</v>
+        <v>5.707801020169398</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.1467</t>
+          <t>X &lt; -0.1465</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.434746620068061</v>
+        <v>1.543942229167072</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1764394729957672</v>
+        <v>-0.03923485598878074</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.440837335020269</v>
+        <v>2.269729858399216</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.571062478608631</v>
+        <v>2.699914199914197</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.840001841175592</v>
+        <v>3.712166560463778</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.534966232256465</v>
+        <v>3.684651778982399</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.751460692267408</v>
+        <v>3.924295990057246</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.079572771372234</v>
+        <v>2.257262028472695</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.621000253403665</v>
+        <v>2.820890019936506</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.771081457073805</v>
+        <v>1.997061439121524</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.771199575922054</v>
+        <v>2.871107611940729</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.106782547554488</v>
+        <v>3.230479168582733</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.084222055686858</v>
+        <v>2.232911603464686</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.487404653825884</v>
+        <v>2.18075164620295</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.1227</t>
+          <t>X &lt; -0.1225</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.364898947439222</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4497180176379203</v>
+        <v>-0.8465356632895933</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.908269979505505</v>
+        <v>2.87228046094981</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.838041900721869</v>
+        <v>1.919913419913421</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.848424913997853</v>
+        <v>2.729365577662797</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.165185557450812</v>
+        <v>2.259365321157986</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.53994797473058</v>
+        <v>1.452693953237812</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.03823178016725848</v>
+        <v>0.01973037917634457</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5674527299766297</v>
+        <v>0.5397879571750579</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2824660663532299</v>
+        <v>-0.3810278098648752</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8461661087199133</v>
+        <v>0.8525068932765976</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.453174798071025</v>
+        <v>1.255767133629725</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.715353725222144</v>
+        <v>0.3261656770276602</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.187993338376124</v>
+        <v>1.456267807765499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.09869</t>
+          <t>X &lt; -0.09853</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.05072953908589994</v>
+        <v>0.06399113923158239</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8432907131386003</v>
+        <v>-1.05116722517544</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9099518884721789</v>
+        <v>0.8951883902540061</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9692657846786972</v>
+        <v>1.025072431468686</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.226081190419706</v>
+        <v>2.966108001905219</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.223807722619831</v>
+        <v>1.138443598971413</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4295468387703494</v>
+        <v>0.2246716007776826</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.9093428912783708</v>
+        <v>-1.096955611459229</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5628891503652582</v>
+        <v>-0.8917849191535225</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.164577712509818</v>
+        <v>-1.630187857419109</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6379353560889527</v>
+        <v>-1.11771835438514</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3529501028539102</v>
+        <v>-0.9725890283757295</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.166846735607351</v>
+        <v>-1.913420560634748</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5283746217818788</v>
+        <v>-1.41938582921378</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.0747</t>
+          <t>X &lt; -0.07455</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.04920445139335783</v>
+        <v>-0.01011182488698381</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.257361472210967</v>
+        <v>-1.355193671947596</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9479091003424358</v>
+        <v>0.8701159587853198</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6614894828772222</v>
+        <v>0.5892218627617893</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>1.955517309781115</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.160011869350299</v>
+        <v>1.101423389302397</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.536172354450116</v>
+        <v>0.2700436515943778</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.321882380950299</v>
+        <v>-1.567161197148124</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5874540015724321</v>
+        <v>-0.9404252521701366</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.614446036579245</v>
+        <v>-2.059335894586738</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.6551889048302186</v>
+        <v>-1.116960043295599</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.041311660780686</v>
+        <v>-1.594234849946261</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.760742153227035</v>
+        <v>-2.405642613402783</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.223023668789828</v>
+        <v>-1.970715501034981</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.05071</t>
+          <t>X &lt; -0.05057</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1076</v>
+        <v>1091</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.139318234391105</v>
+        <v>-0.2456190712637891</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.161955064774652</v>
+        <v>-2.325383198347467</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.037011502833444</v>
+        <v>-1.038751036288581</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2474032006126734</v>
+        <v>0.2295964707408729</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.418426137438992</v>
+        <v>1.244517092814313</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5684877722911352</v>
+        <v>0.4764390166295129</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2963093352109283</v>
+        <v>-0.535901912763606</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.082799453200742</v>
+        <v>-1.317050661610274</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1686969256919966</v>
+        <v>-0.4837832664886079</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.060243844131001</v>
+        <v>-1.531672774544205</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1762042098423535</v>
+        <v>-0.3149455586942764</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.4791753843586974</v>
+        <v>-1.029102616930778</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.126112318019672</v>
+        <v>-1.648548302091598</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3840898598142104</v>
+        <v>-1.074248188148211</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02672</t>
+          <t>X &lt; -0.02659</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.171644976040362</v>
+        <v>-1.107587280707456</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.534028469207243</v>
+        <v>-2.514341541621782</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.333081871216436</v>
+        <v>-1.256689819705848</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.377924960509532</v>
+        <v>-1.300220861359307</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2462509057952644</v>
+        <v>-0.2753652751693281</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6202911609527391</v>
+        <v>-0.6679062681569192</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.661663017925186</v>
+        <v>-1.746938624839345</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.806526390567143</v>
+        <v>-1.893611889843079</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.61601899797909</v>
+        <v>-1.752018572718214</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.14286492675209</v>
+        <v>-2.326457563296557</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.16872262177823</v>
+        <v>-1.362777079366879</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.237699517653567</v>
+        <v>-1.477894963989968</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.261709851814665</v>
+        <v>-1.551533106066508</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.424982053122747</v>
+        <v>-1.758998863265923</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.002725</t>
+          <t>X &lt; -0.002611</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1734</v>
+        <v>1746</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.82264470826761</v>
+        <v>-1.799480784523141</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.946626751318689</v>
+        <v>-2.955632482284024</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.082862047035164</v>
+        <v>-3.092604587600569</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.037841025315309</v>
+        <v>-3.047347868532384</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.112379111205364</v>
+        <v>-2.196819348522126</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.416163199362089</v>
+        <v>-2.464142397177788</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.619666550765622</v>
+        <v>-3.693018986071195</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.252791167140444</v>
+        <v>-3.330688936190597</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.168921942568254</v>
+        <v>-3.280985699300714</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.528598274510756</v>
+        <v>-3.675182233122143</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.897069354722809</v>
+        <v>-3.048970642759031</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.774345651879194</v>
+        <v>-2.960417139762782</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.10604911545304</v>
+        <v>-3.325153513327614</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.080114694414561</v>
+        <v>-3.332021094243373</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.02127</t>
+          <t>X &lt; 0.02137</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2058</v>
+        <v>2070</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.02220043420408</v>
+        <v>-1.958023490753526</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.497899225047462</v>
+        <v>-2.508274500820939</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.62607118839189</v>
+        <v>-2.636954817627128</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.470768287395416</v>
+        <v>-2.482142857142854</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.726094182979089</v>
+        <v>-1.79203894374173</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.322636492291295</v>
+        <v>-2.359939491787884</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.205276668799137</v>
+        <v>-3.262091167442094</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.920660720735732</v>
+        <v>-2.980634827921271</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.859379822401245</v>
+        <v>-2.944296853684101</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.344433950823543</v>
+        <v>-3.453664117679246</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.84427542451639</v>
+        <v>-2.957125726623374</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.589790151006753</v>
+        <v>-2.728491850629254</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.886754614471187</v>
+        <v>-3.049589720033076</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.586303724648509</v>
+        <v>-2.726413245246917</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.04526</t>
+          <t>X &lt; 0.04535</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2339</v>
+        <v>2353</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.247922833255444</v>
+        <v>-1.19988359158183</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.986615096801074</v>
+        <v>-1.915699058034384</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.976235210480887</v>
+        <v>-1.906654647934531</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.866226908826164</v>
+        <v>-1.796838159724324</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.700730081403989</v>
+        <v>-1.713453810118494</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.147627799601693</v>
+        <v>-2.095842819809526</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.678864187815584</v>
+        <v>-2.685110026128434</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.867892997888177</v>
+        <v>-2.874576041050823</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.821246549507634</v>
+        <v>-2.80458278110882</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.26468259786553</v>
+        <v>-3.351647473439748</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.891759690691799</v>
+        <v>-2.981675336491371</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.791865440381876</v>
+        <v>-2.900925430706145</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.060974113605695</v>
+        <v>-3.188519234585904</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.897833699125322</v>
+        <v>-3.044313510300675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.06925</t>
+          <t>X &lt; 0.06933</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2652</v>
+        <v>2665</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.524068000515591</v>
+        <v>-1.501896739001992</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.99000002149608</v>
+        <v>-2.020072623154526</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.689276812896971</v>
+        <v>-1.646967107625102</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.065138222015051</v>
+        <v>-2.020694259012025</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.794599699145785</v>
+        <v>-1.779825057182293</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.85320298596983</v>
+        <v>-1.823887062889767</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.181334044407762</v>
+        <v>-2.164202688261796</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.290050189999214</v>
+        <v>-2.273438645994354</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.33113799473378</v>
+        <v>-2.328079173976512</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.746990832082815</v>
+        <v>-2.757449534947334</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.517299051355415</v>
+        <v>-2.529354807451988</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.424990361716361</v>
+        <v>-2.451077203135867</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.56100794081631</v>
+        <v>-2.601052911760505</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.352583863077506</v>
+        <v>-2.406829447402245</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.09324</t>
+          <t>X &lt; 0.09331</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2885</v>
+        <v>2897</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.20417344944395</v>
+        <v>-1.169905639319978</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.831142510205012</v>
+        <v>-1.80727997226353</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.586321022165372</v>
+        <v>-1.564055784189726</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.955957518478158</v>
+        <v>-1.931962258587653</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.750501152138369</v>
+        <v>-1.749351392451281</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.745852861609499</v>
+        <v>-1.733675326091692</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.985178811806982</v>
+        <v>-1.982747416986165</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.19188872317045</v>
+        <v>-2.189313379177456</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.372954805586616</v>
+        <v>-2.38034843423096</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.823829860053472</v>
+        <v>-2.841282592604102</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.559958852806716</v>
+        <v>-2.578830069820803</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.645530480101684</v>
+        <v>-2.674652222798592</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.943163995795572</v>
+        <v>-2.982359418511415</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.768136299223272</v>
+        <v>-2.818395789241279</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.1172</t>
+          <t>X &lt; 0.1173</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3090</v>
+        <v>3102</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.885685608362266</v>
+        <v>-0.8568212951919563</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.513120821212631</v>
+        <v>-1.492132840678671</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.4394694451478</v>
+        <v>-1.419246622096693</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.679229009926154</v>
+        <v>-1.690047741461619</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.490613942384591</v>
+        <v>-1.519487465790064</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.627906044455287</v>
+        <v>-1.615407122362669</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.663223553271422</v>
+        <v>-1.691194057726143</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.887068989469583</v>
+        <v>-1.914767143556475</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.833911477526513</v>
+        <v>-1.870251072878226</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.117128136309418</v>
+        <v>-2.161797999840942</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.013409276558676</v>
+        <v>-2.026550653973167</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.123192981989305</v>
+        <v>-2.144241363028257</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.493487033663101</v>
+        <v>-2.522008819445134</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.347312150210136</v>
+        <v>-2.384511339977756</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.1412</t>
+          <t>X &lt; 0.1413</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3246</v>
+        <v>3258</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6858868804883258</v>
+        <v>-0.6605245427102844</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.298977507269143</v>
+        <v>-1.279833252550482</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.278399452473579</v>
+        <v>-1.259740266359991</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.653945662062164</v>
+        <v>-1.633764644168572</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.223662956263013</v>
+        <v>-1.219211098186605</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.186377655896024</v>
+        <v>-1.174953692992936</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.131705541681612</v>
+        <v>-1.127371297444647</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.459305990909364</v>
+        <v>-1.45426199555132</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.319214620240395</v>
+        <v>-1.321560736060064</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.660243844131003</v>
+        <v>-1.669051025274207</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.540414377583566</v>
+        <v>-1.549888238988295</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.673916603730461</v>
+        <v>-1.689692314897208</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.923276988843597</v>
+        <v>-1.945415697762321</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.803909964398166</v>
+        <v>-1.833093790793662</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.1652</t>
+          <t>X &lt; 0.1653</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3384</v>
+        <v>3395</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4938686357742768</v>
+        <v>-0.485463937563047</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.735211664234221</v>
+        <v>-0.7325609969227926</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9375362476757516</v>
+        <v>-0.9344725824444495</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.262953609314067</v>
+        <v>-1.258758128802185</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.9308942986445246</v>
+        <v>-0.9392239604919652</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9124223787915042</v>
+        <v>-0.9150698939099939</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8633417791931919</v>
+        <v>-0.8717699171197708</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.049047906027631</v>
+        <v>-1.057166778458303</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.005544876659215</v>
+        <v>-1.019420879197924</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.219629912607992</v>
+        <v>-1.23891946676229</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.171942345172418</v>
+        <v>-1.191523134706841</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.357560352693888</v>
+        <v>-1.382113090355887</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.554705886510291</v>
+        <v>-1.584478096678644</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.48999387345372</v>
+        <v>-1.52544279281971</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3525</v>
+        <v>3536</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2197515308169997</v>
+        <v>-0.2136902976962247</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2894445041466724</v>
+        <v>-0.2883283688928913</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4993169472672534</v>
+        <v>-0.497740177184717</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9195903732514239</v>
+        <v>-0.916646523245511</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6221591968645157</v>
+        <v>-0.6291846638211567</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5924690679593994</v>
+        <v>-0.595051174535449</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6335766257475797</v>
+        <v>-0.6404719955405511</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.802132469301597</v>
+        <v>-0.8087345157847139</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7344043679144718</v>
+        <v>-0.7456530834605957</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.8604705372452059</v>
+        <v>-0.8761507561245736</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.8511128028447175</v>
+        <v>-0.8669301565392331</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9427868670475092</v>
+        <v>-0.9627209921506577</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.177093199662387</v>
+        <v>-1.200925526224559</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.105833116952539</v>
+        <v>-1.134205013013101</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3657</v>
+        <v>3669</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1920876926596904</v>
+        <v>-0.2015838509597714</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.1264439061002207</v>
+        <v>-0.1133921428600004</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5610283611340208</v>
+        <v>-0.5468095070531973</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8796917244594269</v>
+        <v>-0.864345901448381</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5577857083679163</v>
+        <v>-0.5505790562785791</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5184370123728073</v>
+        <v>-0.5077919565671181</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4792174789326822</v>
+        <v>-0.4721298155089286</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5765883185237968</v>
+        <v>-0.5694830839866967</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4861306185275254</v>
+        <v>-0.4827402298015357</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6382280014650661</v>
+        <v>-0.6382719612540768</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5818848931015808</v>
+        <v>-0.5822482953485633</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6689379896915213</v>
+        <v>-0.6723837130719232</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8552010275701747</v>
+        <v>-0.8617011800946202</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8056219218676333</v>
+        <v>-0.8155343973990981</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3740</v>
+        <v>3751</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2560292732734979</v>
+        <v>-0.2518759056521347</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.1475392238113926</v>
+        <v>-0.1469694840529385</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4212909970229077</v>
+        <v>-0.4200412524245252</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7033150314315293</v>
+        <v>-0.701200288677029</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3203847036701077</v>
+        <v>-0.3251154023501002</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3286204517260032</v>
+        <v>-0.3304567053998184</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2654074206968602</v>
+        <v>-0.2702391517902996</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3709125655976422</v>
+        <v>-0.3755810887994784</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2303517500708381</v>
+        <v>-0.2382393970203864</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3711412800284393</v>
+        <v>-0.3816688224316351</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2937988629308776</v>
+        <v>-0.3046214096330502</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3780815480583257</v>
+        <v>-0.3914425711339291</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.462532726070485</v>
+        <v>-0.4785739977889421</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.4891531761174122</v>
+        <v>-0.5078486627909697</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3793</v>
+        <v>3803</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.08995439101779823</v>
+        <v>-0.07300490664798787</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.005374134110667228</v>
+        <v>-0.01727318265096045</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2544865472596385</v>
+        <v>-0.2657369140890609</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4518363742310711</v>
+        <v>-0.4625716533663109</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.186889522279273</v>
+        <v>-0.2031600988293079</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2171376845948387</v>
+        <v>-0.2309142725059843</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1033268790705861</v>
+        <v>-0.1198268729632588</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2138335467140138</v>
+        <v>-0.2300506977478705</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1550327887174134</v>
+        <v>-0.1738326439038005</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3583739468436704</v>
+        <v>-0.3790735611269511</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2849660772067963</v>
+        <v>-0.3058672343704245</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2885378645286352</v>
+        <v>-0.3118636587054056</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3512975662907749</v>
+        <v>-0.3768967149826068</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3743624907710554</v>
+        <v>-0.4023390653152248</v>
       </c>
     </row>
     <row r="29">
@@ -5104,153 +5104,153 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3842</v>
+        <v>3853</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1073751745032183</v>
+        <v>-0.1045246546852212</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.08537582139403099</v>
+        <v>0.08523631634784579</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1655654367207333</v>
+        <v>-0.1650807285852807</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.332764667983966</v>
+        <v>-0.331773972856034</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1299418129527368</v>
+        <v>-0.1338078448063342</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1040573947189714</v>
+        <v>-0.1058520115213852</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1226483706405048</v>
+        <v>-0.1264905477759299</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1337503756858567</v>
+        <v>-0.1376698300507542</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.001528344452559338</v>
+        <v>-0.004875091987237568</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1320067146458257</v>
+        <v>-0.1403105712087438</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.08809194647442808</v>
+        <v>-0.09657223608206777</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.06511419654992778</v>
+        <v>-0.07574182433837251</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.08032998542058323</v>
+        <v>-0.09310236418588147</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1522074565584646</v>
+        <v>-0.1668166701457636</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.3092</t>
+          <t>X &lt; 0.3091</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3891</v>
+        <v>3902</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.04751439119009859</v>
+        <v>-0.04523315311175935</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.03112338929123837</v>
+        <v>-0.03094859323139332</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.0532497256776665</v>
+        <v>-0.05308874348915538</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2166842529986468</v>
+        <v>-0.2160385626643375</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.07442509734772784</v>
+        <v>-0.07779061737374349</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.03182826360833246</v>
+        <v>0.02997408338399765</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.03809517272386387</v>
+        <v>0.03445065738766573</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.04696195860615404</v>
+        <v>0.04320047459538756</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1541513382358133</v>
+        <v>0.1483172680189853</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.06299107242868729</v>
+        <v>0.05548852980668073</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.001105331455740099</v>
+        <v>-0.006266159714392927</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1013108792217636</v>
+        <v>0.09190026279564023</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1324272092920253</v>
+        <v>0.1210822723045268</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1414533105369742</v>
+        <v>0.1283596075202809</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.3332</t>
+          <t>X &lt; 0.3331</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3937</v>
+        <v>3948</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.05053628369891072</v>
+        <v>-0.04861220357923202</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.07350942362896262</v>
+        <v>0.07337775662382739</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.05424939487804181</v>
+        <v>-0.05408928784984113</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1382546480179627</v>
+        <v>-0.1378401790225965</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.07211732795799719</v>
+        <v>0.06894790587287503</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2566819926363877</v>
+        <v>0.2545027219374987</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2619448194454819</v>
+        <v>0.2582785187300374</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2653159978923156</v>
+        <v>0.2615637505285946</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.3397850849990363</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.2452623725652572</v>
+        <v>0.2384961937141767</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1563747945631135</v>
+        <v>0.149820031855775</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1543024061205145</v>
+        <v>0.1462943279543865</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2309481168640133</v>
+        <v>0.221192913053514</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.2679313327040163</v>
+        <v>0.2566418330903062</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3978</v>
+        <v>3989</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.01219346583247471</v>
+        <v>0.01362630604754145</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.09336153554968973</v>
+        <v>0.09316447661049665</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.03713673221884761</v>
+        <v>-0.03702689835754569</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.06878477399254734</v>
+        <v>-0.06857071410709636</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1088243093779724</v>
+        <v>0.1060842400242805</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.3196463475999209</v>
+        <v>0.3175618970063567</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2487169695723495</v>
+        <v>0.2456173113785667</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.272343855709579</v>
+        <v>0.2691161855083379</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3759164786864204</v>
+        <v>0.3711944555689399</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3435733331668374</v>
+        <v>0.3376258953884559</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2283983786688353</v>
+        <v>0.2227385847296759</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2518452102656354</v>
+        <v>0.2449213019369978</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2982644529713951</v>
+        <v>0.2899517943032208</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2869334823221905</v>
+        <v>0.2774754680382898</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4010</v>
+        <v>4021</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.01721968907787641</v>
+        <v>0.01839585979323033</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1346507356758124</v>
+        <v>0.1343332074875363</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.02692902832919941</v>
+        <v>0.0268619905313443</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.07121233175255526</v>
+        <v>0.07103873551405115</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1685107011989118</v>
+        <v>0.1660149497960433</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.305372896244414</v>
+        <v>0.3035342504337564</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2343301836759011</v>
+        <v>0.2316758624818078</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2042427660921433</v>
+        <v>0.2016181054337025</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2815803071179062</v>
+        <v>0.2777358374380583</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2925214772441791</v>
+        <v>0.287550686132505</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1766199116382055</v>
+        <v>0.1719411648401987</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1502905776809698</v>
+        <v>0.1446833379821797</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1680307384358102</v>
+        <v>0.1613234108134165</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1336214381490635</v>
+        <v>0.126026902912443</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4028</v>
+        <v>4039</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.006092135761115003</v>
+        <v>0.007163594658919692</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1653236189760818</v>
+        <v>0.1649189398707591</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.08108885856928794</v>
+        <v>0.08087433621036411</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1010039383554968</v>
+        <v>0.1007479801008984</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2202466251169071</v>
+        <v>0.2178372509170714</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3082834854117991</v>
+        <v>0.3065516625576024</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2619636707239792</v>
+        <v>0.2594596262589377</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.254722552449941</v>
+        <v>0.252191444910153</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3066598269818854</v>
+        <v>0.3030903211278968</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2641609177737578</v>
+        <v>0.2597317275152875</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.147855791456486</v>
+        <v>0.1437210742014443</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1466043658450147</v>
+        <v>0.1415831241227821</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1623872854816923</v>
+        <v>0.1563876860126925</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1291390988136882</v>
+        <v>0.1223571372436112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.4291</t>
+          <t>X &lt; 0.429</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4047</v>
+        <v>4057</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01786184334223861</v>
+        <v>-0.02853934331450603</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1330764918243403</v>
+        <v>0.1215058798318296</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1213078617798473</v>
+        <v>0.1098265923012605</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.141749466144681</v>
+        <v>0.1301942463732502</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.3072317073859949</v>
+        <v>0.2937949177930648</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3222881462998117</v>
+        <v>0.3095423522124605</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2757918600564651</v>
+        <v>0.2623909748057685</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.291071616493646</v>
+        <v>0.27770432654237</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.3178092068878939</v>
+        <v>0.3036016828549606</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2715260892187885</v>
+        <v>0.256783855455609</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1794994420532419</v>
+        <v>0.1650122947112251</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1290281116830627</v>
+        <v>0.1138737966144348</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1921676721447838</v>
+        <v>0.1761384289529317</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1354330691900714</v>
+        <v>0.1187199354308461</v>
       </c>
     </row>
   </sheetData>
